--- a/AAII_Financials/Quarterly/MOGU_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MOGU_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="92">
   <si>
     <t>MOGU</t>
   </si>
@@ -656,328 +656,341 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45016</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44834</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44651</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44469</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44377</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44286</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44196</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44104</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44012</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>43921</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>43830</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>43738</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>43646</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43555</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43465</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43373</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43281</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43190</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43100</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43008</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>42916</v>
       </c>
-      <c r="Y7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>16200</v>
+        <v>11600</v>
       </c>
       <c r="E8" s="3">
-        <v>15900</v>
+        <v>16300</v>
       </c>
       <c r="F8" s="3">
-        <v>23200</v>
+        <v>16000</v>
       </c>
       <c r="G8" s="3">
-        <v>10700</v>
+        <v>23400</v>
       </c>
       <c r="H8" s="3">
-        <v>12700</v>
+        <v>10800</v>
       </c>
       <c r="I8" s="3">
+        <v>12800</v>
+      </c>
+      <c r="J8" s="3">
         <v>12600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>20200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>16000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>18400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>17500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>42200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>30500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>38800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>33100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>53300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>33900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>35800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>26900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>45300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>32000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>39300</v>
       </c>
-      <c r="Y8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E9" s="3">
         <v>7500</v>
       </c>
-      <c r="E9" s="3">
-        <v>8200</v>
-      </c>
       <c r="F9" s="3">
+        <v>8300</v>
+      </c>
+      <c r="G9" s="3">
+        <v>10400</v>
+      </c>
+      <c r="H9" s="3">
+        <v>5800</v>
+      </c>
+      <c r="I9" s="3">
+        <v>6000</v>
+      </c>
+      <c r="J9" s="3">
+        <v>5300</v>
+      </c>
+      <c r="K9" s="3">
+        <v>7000</v>
+      </c>
+      <c r="L9" s="3">
+        <v>6500</v>
+      </c>
+      <c r="M9" s="3">
+        <v>6800</v>
+      </c>
+      <c r="N9" s="3">
+        <v>8600</v>
+      </c>
+      <c r="O9" s="3">
+        <v>15400</v>
+      </c>
+      <c r="P9" s="3">
+        <v>11700</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>9500</v>
+      </c>
+      <c r="R9" s="3">
+        <v>9300</v>
+      </c>
+      <c r="S9" s="3">
+        <v>14600</v>
+      </c>
+      <c r="T9" s="3">
+        <v>11500</v>
+      </c>
+      <c r="U9" s="3">
         <v>10300</v>
       </c>
-      <c r="G9" s="3">
-        <v>5800</v>
-      </c>
-      <c r="H9" s="3">
-        <v>6000</v>
-      </c>
-      <c r="I9" s="3">
-        <v>5200</v>
-      </c>
-      <c r="J9" s="3">
-        <v>7000</v>
-      </c>
-      <c r="K9" s="3">
-        <v>6500</v>
-      </c>
-      <c r="L9" s="3">
-        <v>6800</v>
-      </c>
-      <c r="M9" s="3">
-        <v>8600</v>
-      </c>
-      <c r="N9" s="3">
-        <v>15400</v>
-      </c>
-      <c r="O9" s="3">
-        <v>11700</v>
-      </c>
-      <c r="P9" s="3">
-        <v>9500</v>
-      </c>
-      <c r="Q9" s="3">
-        <v>9300</v>
-      </c>
-      <c r="R9" s="3">
-        <v>14600</v>
-      </c>
-      <c r="S9" s="3">
-        <v>11500</v>
-      </c>
-      <c r="T9" s="3">
-        <v>10300</v>
-      </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>10900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>12300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>11600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>12000</v>
       </c>
-      <c r="Y9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>8700</v>
+        <v>4700</v>
       </c>
       <c r="E10" s="3">
-        <v>7600</v>
+        <v>8800</v>
       </c>
       <c r="F10" s="3">
-        <v>12900</v>
+        <v>7700</v>
       </c>
       <c r="G10" s="3">
-        <v>4900</v>
+        <v>13000</v>
       </c>
       <c r="H10" s="3">
+        <v>5000</v>
+      </c>
+      <c r="I10" s="3">
         <v>6700</v>
       </c>
-      <c r="I10" s="3">
-        <v>7300</v>
-      </c>
       <c r="J10" s="3">
+        <v>7400</v>
+      </c>
+      <c r="K10" s="3">
         <v>13200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>9500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>11700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>8900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>26800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>18800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>29400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>23800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>38700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>22500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>25600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>16000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>33000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>20400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>27300</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1003,79 +1016,83 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E12" s="3">
         <v>2200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>2900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>5200</v>
       </c>
-      <c r="G12" s="3">
-        <v>3200</v>
-      </c>
       <c r="H12" s="3">
+        <v>3300</v>
+      </c>
+      <c r="I12" s="3">
         <v>3000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>2700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>3800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>3900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>4000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>4800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>5000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>7700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>8800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>8700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>8000</v>
-      </c>
-      <c r="S12" s="3">
-        <v>8800</v>
       </c>
       <c r="T12" s="3">
         <v>8800</v>
       </c>
       <c r="U12" s="3">
+        <v>8800</v>
+      </c>
+      <c r="V12" s="3">
         <v>10000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>10500</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>11300</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>10800</v>
       </c>
-      <c r="Y12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1145,25 +1162,28 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>11700</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E14" s="3">
+        <v>11800</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3">
         <v>6800</v>
       </c>
-      <c r="G14" s="3">
-        <v>25800</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
+      <c r="H14" s="3">
+        <v>25900</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
@@ -1177,20 +1197,20 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>216400</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1198,85 +1218,88 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>-2000</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3" t="s">
-        <v>3</v>
+      <c r="X14" s="3">
+        <v>0</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>5500</v>
+        <v>300</v>
       </c>
       <c r="E15" s="3">
+        <v>5600</v>
+      </c>
+      <c r="F15" s="3">
         <v>2800</v>
       </c>
-      <c r="F15" s="3">
-        <v>23200</v>
-      </c>
       <c r="G15" s="3">
-        <v>13200</v>
+        <v>23400</v>
       </c>
       <c r="H15" s="3">
-        <v>8900</v>
+        <v>13300</v>
       </c>
       <c r="I15" s="3">
-        <v>11300</v>
+        <v>9000</v>
       </c>
       <c r="J15" s="3">
+        <v>11400</v>
+      </c>
+      <c r="K15" s="3">
         <v>15700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>10800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>9800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>12800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>16100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>11800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>10100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>6800</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>9700</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>8000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>3900</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>7900</v>
-      </c>
-      <c r="V15" s="3">
-        <v>16300</v>
       </c>
       <c r="W15" s="3">
         <v>16300</v>
@@ -1284,11 +1307,14 @@
       <c r="X15" s="3">
         <v>16300</v>
       </c>
-      <c r="Y15" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>16300</v>
+      </c>
+      <c r="Z15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1311,150 +1337,157 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>35400</v>
+        <v>18800</v>
       </c>
       <c r="E17" s="3">
-        <v>22500</v>
+        <v>35700</v>
       </c>
       <c r="F17" s="3">
-        <v>56400</v>
+        <v>22600</v>
       </c>
       <c r="G17" s="3">
-        <v>56600</v>
+        <v>56800</v>
       </c>
       <c r="H17" s="3">
-        <v>26200</v>
+        <v>56900</v>
       </c>
       <c r="I17" s="3">
-        <v>27800</v>
+        <v>26400</v>
       </c>
       <c r="J17" s="3">
+        <v>28000</v>
+      </c>
+      <c r="K17" s="3">
         <v>37300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>30300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>31700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>39500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>291900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>64900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>55300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>58700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>67500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>61800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>52100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>47900</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W17" s="3">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X17" s="3">
         <v>76000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>69400</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-19300</v>
+        <v>-7200</v>
       </c>
       <c r="E18" s="3">
-        <v>-6600</v>
+        <v>-19400</v>
       </c>
       <c r="F18" s="3">
-        <v>-33200</v>
+        <v>-6700</v>
       </c>
       <c r="G18" s="3">
-        <v>-45900</v>
+        <v>-33400</v>
       </c>
       <c r="H18" s="3">
-        <v>-13500</v>
+        <v>-46200</v>
       </c>
       <c r="I18" s="3">
-        <v>-15200</v>
+        <v>-13600</v>
       </c>
       <c r="J18" s="3">
+        <v>-15300</v>
+      </c>
+      <c r="K18" s="3">
         <v>-17000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-14300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-13200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-22000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-249700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-34400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-16400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-25600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-14200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-27900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-16300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-20900</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W18" s="3">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X18" s="3">
         <v>-44000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-30100</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1480,8 +1513,9 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1489,141 +1523,147 @@
         <v>1200</v>
       </c>
       <c r="E20" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F20" s="3">
         <v>-1500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>300</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>13300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-4100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-3900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>5700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>23700</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W20" s="3">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X20" s="3">
         <v>1900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>900</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-15100</v>
+        <v>-5300</v>
       </c>
       <c r="E21" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="F21" s="3">
         <v>-5100</v>
       </c>
-      <c r="F21" s="3">
-        <v>-23100</v>
-      </c>
       <c r="G21" s="3">
-        <v>-39900</v>
+        <v>-23300</v>
       </c>
       <c r="H21" s="3">
+        <v>-40200</v>
+      </c>
+      <c r="I21" s="3">
         <v>-4100</v>
       </c>
-      <c r="I21" s="3">
-        <v>-20000</v>
-      </c>
       <c r="J21" s="3">
+        <v>-20100</v>
+      </c>
+      <c r="K21" s="3">
         <v>1800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-12700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-2500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-23400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-249700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-36400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-3300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-11600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-18100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-10700</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X21" s="3">
         <v>-23300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-10300</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1693,105 +1733,111 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-18000</v>
+        <v>-6100</v>
       </c>
       <c r="E23" s="3">
-        <v>-8100</v>
+        <v>-18100</v>
       </c>
       <c r="F23" s="3">
-        <v>-33300</v>
+        <v>-8200</v>
       </c>
       <c r="G23" s="3">
-        <v>-44100</v>
+        <v>-33500</v>
       </c>
       <c r="H23" s="3">
-        <v>-13200</v>
+        <v>-44400</v>
       </c>
       <c r="I23" s="3">
-        <v>-15300</v>
+        <v>-13300</v>
       </c>
       <c r="J23" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="K23" s="3">
         <v>-3800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-13500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-12500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-21100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-253800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-38300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-15100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-24200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-8500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-26600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-15200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-26800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-42100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-29200</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="E24" s="3">
         <v>-100</v>
       </c>
       <c r="F24" s="3">
+        <v>-200</v>
+      </c>
+      <c r="G24" s="3">
         <v>-1800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-200</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
       <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
         <v>-300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1300</v>
-      </c>
-      <c r="K24" s="3">
-        <v>-200</v>
       </c>
       <c r="L24" s="3">
         <v>-200</v>
@@ -1800,43 +1846,46 @@
         <v>-200</v>
       </c>
       <c r="N24" s="3">
+        <v>-200</v>
+      </c>
+      <c r="O24" s="3">
         <v>100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-1700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-3700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-3900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-3800</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1906,150 +1955,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-17900</v>
+        <v>-5800</v>
       </c>
       <c r="E26" s="3">
+        <v>-18000</v>
+      </c>
+      <c r="F26" s="3">
         <v>-8000</v>
       </c>
-      <c r="F26" s="3">
-        <v>-31500</v>
-      </c>
       <c r="G26" s="3">
-        <v>-43900</v>
+        <v>-31700</v>
       </c>
       <c r="H26" s="3">
-        <v>-13200</v>
+        <v>-44200</v>
       </c>
       <c r="I26" s="3">
-        <v>-15000</v>
+        <v>-13300</v>
       </c>
       <c r="J26" s="3">
+        <v>-15100</v>
+      </c>
+      <c r="K26" s="3">
         <v>-5100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-13300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-12400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-20900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-254000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-38200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-15200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-23400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-8300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-25800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-14500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>4400</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W26" s="3">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X26" s="3">
         <v>-38200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-25300</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-16600</v>
+        <v>-4900</v>
       </c>
       <c r="E27" s="3">
-        <v>-7900</v>
+        <v>-16800</v>
       </c>
       <c r="F27" s="3">
-        <v>-31200</v>
+        <v>-8000</v>
       </c>
       <c r="G27" s="3">
-        <v>-44000</v>
+        <v>-31400</v>
       </c>
       <c r="H27" s="3">
-        <v>-13200</v>
+        <v>-44300</v>
       </c>
       <c r="I27" s="3">
-        <v>-15000</v>
+        <v>-13300</v>
       </c>
       <c r="J27" s="3">
+        <v>-15100</v>
+      </c>
+      <c r="K27" s="3">
         <v>-5100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-13300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-12400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-20900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-255900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-50300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-18800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-21400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-26300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-65900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-43300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>3700</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W27" s="3">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X27" s="3">
         <v>-63300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-49600</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2119,8 +2177,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2190,8 +2251,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2261,8 +2325,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2332,8 +2399,11 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2341,141 +2411,147 @@
         <v>-1200</v>
       </c>
       <c r="E32" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F32" s="3">
         <v>1500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-300</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-13300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>4100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>3900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-5700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-23700</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W32" s="3">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X32" s="3">
         <v>-1900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-900</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-16600</v>
+        <v>-4900</v>
       </c>
       <c r="E33" s="3">
-        <v>-7900</v>
+        <v>-16800</v>
       </c>
       <c r="F33" s="3">
-        <v>-31200</v>
+        <v>-8000</v>
       </c>
       <c r="G33" s="3">
-        <v>-44000</v>
+        <v>-31400</v>
       </c>
       <c r="H33" s="3">
-        <v>-13200</v>
+        <v>-44300</v>
       </c>
       <c r="I33" s="3">
-        <v>-15000</v>
+        <v>-13300</v>
       </c>
       <c r="J33" s="3">
+        <v>-15100</v>
+      </c>
+      <c r="K33" s="3">
         <v>-5100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-13300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-12400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-20900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-255900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-50300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-18800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-21400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-26300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-65900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-43300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>3700</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W33" s="3">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X33" s="3">
         <v>-63300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-49600</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2545,155 +2621,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-16600</v>
+        <v>-4900</v>
       </c>
       <c r="E35" s="3">
-        <v>-7900</v>
+        <v>-16800</v>
       </c>
       <c r="F35" s="3">
-        <v>-31200</v>
+        <v>-8000</v>
       </c>
       <c r="G35" s="3">
-        <v>-44000</v>
+        <v>-31400</v>
       </c>
       <c r="H35" s="3">
-        <v>-13200</v>
+        <v>-44300</v>
       </c>
       <c r="I35" s="3">
-        <v>-15000</v>
+        <v>-13300</v>
       </c>
       <c r="J35" s="3">
+        <v>-15100</v>
+      </c>
+      <c r="K35" s="3">
         <v>-5100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-13300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-12400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-20900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-255900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-50300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-18800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-21400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-26300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-65900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-43300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>3700</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W35" s="3">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X35" s="3">
         <v>-63300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-49600</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45016</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44834</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44651</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44469</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44377</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44286</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44196</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44104</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44012</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>43921</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>43830</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>43738</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>43646</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43555</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43465</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43373</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43281</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43190</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43100</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43008</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>42916</v>
       </c>
-      <c r="Y38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2719,8 +2804,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2746,65 +2832,66 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>57500</v>
+        <v>50900</v>
       </c>
       <c r="E41" s="3">
-        <v>54300</v>
+        <v>57900</v>
       </c>
       <c r="F41" s="3">
-        <v>60600</v>
+        <v>54600</v>
       </c>
       <c r="G41" s="3">
-        <v>70000</v>
+        <v>61000</v>
       </c>
       <c r="H41" s="3">
-        <v>83200</v>
+        <v>70500</v>
       </c>
       <c r="I41" s="3">
-        <v>74800</v>
+        <v>83700</v>
       </c>
       <c r="J41" s="3">
+        <v>75400</v>
+      </c>
+      <c r="K41" s="3">
         <v>91000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>81300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>115200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>126200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>135500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>138300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>177500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>194200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>183900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>129500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>166400</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2817,65 +2904,68 @@
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>20100</v>
+        <v>14400</v>
       </c>
       <c r="E42" s="3">
-        <v>29100</v>
+        <v>20300</v>
       </c>
       <c r="F42" s="3">
-        <v>27200</v>
+        <v>29300</v>
       </c>
       <c r="G42" s="3">
-        <v>15000</v>
+        <v>27400</v>
       </c>
       <c r="H42" s="3">
-        <v>23900</v>
+        <v>15100</v>
       </c>
       <c r="I42" s="3">
-        <v>35900</v>
+        <v>24100</v>
       </c>
       <c r="J42" s="3">
+        <v>36200</v>
+      </c>
+      <c r="K42" s="3">
         <v>22100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>32700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>30600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>35100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>50900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>59900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>50500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>32200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>50400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>44400</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>32200</v>
       </c>
-      <c r="U42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2888,65 +2978,68 @@
       <c r="Y42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>600</v>
+      </c>
+      <c r="E43" s="3">
         <v>1200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1500</v>
       </c>
-      <c r="F43" s="3">
-        <v>5000</v>
-      </c>
       <c r="G43" s="3">
-        <v>11500</v>
+        <v>5100</v>
       </c>
       <c r="H43" s="3">
-        <v>13600</v>
+        <v>11600</v>
       </c>
       <c r="I43" s="3">
-        <v>17600</v>
+        <v>13700</v>
       </c>
       <c r="J43" s="3">
+        <v>17700</v>
+      </c>
+      <c r="K43" s="3">
         <v>19400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>16100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>16500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>16700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>27900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>21600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>18900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>18700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>19200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>27400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>30000</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2959,8 +3052,11 @@
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2983,40 +3079,40 @@
         <v>0</v>
       </c>
       <c r="J44" s="3">
+        <v>0</v>
+      </c>
+      <c r="K44" s="3">
         <v>100</v>
-      </c>
-      <c r="K44" s="3">
-        <v>300</v>
       </c>
       <c r="L44" s="3">
         <v>300</v>
       </c>
       <c r="M44" s="3">
+        <v>300</v>
+      </c>
+      <c r="N44" s="3">
         <v>400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>500</v>
-      </c>
-      <c r="P44" s="3">
-        <v>800</v>
       </c>
       <c r="Q44" s="3">
         <v>800</v>
       </c>
       <c r="R44" s="3">
+        <v>800</v>
+      </c>
+      <c r="S44" s="3">
         <v>700</v>
-      </c>
-      <c r="S44" s="3">
-        <v>100</v>
       </c>
       <c r="T44" s="3">
         <v>100</v>
       </c>
-      <c r="U44" s="3" t="s">
-        <v>3</v>
+      <c r="U44" s="3">
+        <v>100</v>
       </c>
       <c r="V44" s="3" t="s">
         <v>3</v>
@@ -3030,65 +3126,68 @@
       <c r="Y44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>13900</v>
+      </c>
+      <c r="E45" s="3">
         <v>9700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>7600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>6500</v>
       </c>
-      <c r="G45" s="3">
-        <v>8500</v>
-      </c>
       <c r="H45" s="3">
-        <v>9100</v>
+        <v>8600</v>
       </c>
       <c r="I45" s="3">
-        <v>7900</v>
+        <v>9200</v>
       </c>
       <c r="J45" s="3">
+        <v>8000</v>
+      </c>
+      <c r="K45" s="3">
         <v>13800</v>
-      </c>
-      <c r="K45" s="3">
-        <v>11800</v>
       </c>
       <c r="L45" s="3">
         <v>11800</v>
       </c>
       <c r="M45" s="3">
+        <v>11800</v>
+      </c>
+      <c r="N45" s="3">
         <v>14700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>18600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>22100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>24400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>24700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>23900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>7300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>6300</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3101,65 +3200,68 @@
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>88500</v>
+        <v>79800</v>
       </c>
       <c r="E46" s="3">
-        <v>92400</v>
+        <v>89100</v>
       </c>
       <c r="F46" s="3">
-        <v>99300</v>
+        <v>93100</v>
       </c>
       <c r="G46" s="3">
-        <v>105000</v>
+        <v>99900</v>
       </c>
       <c r="H46" s="3">
-        <v>129800</v>
+        <v>105700</v>
       </c>
       <c r="I46" s="3">
-        <v>136300</v>
+        <v>130700</v>
       </c>
       <c r="J46" s="3">
+        <v>137200</v>
+      </c>
+      <c r="K46" s="3">
         <v>146400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>142100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>174500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>193100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>235000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>242400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>272100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>270600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>278000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>208700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>234900</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3172,65 +3274,68 @@
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>11400</v>
+      </c>
+      <c r="E47" s="3">
         <v>9600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>8500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>10000</v>
       </c>
-      <c r="G47" s="3">
-        <v>10900</v>
-      </c>
       <c r="H47" s="3">
-        <v>10100</v>
+        <v>11000</v>
       </c>
       <c r="I47" s="3">
+        <v>10200</v>
+      </c>
+      <c r="J47" s="3">
         <v>9200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>8600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>17200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>15900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>15100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>11300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>17300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>34200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>36800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>32000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>29200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>27600</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3243,65 +3348,68 @@
       <c r="Y47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>27600</v>
+        <v>31200</v>
       </c>
       <c r="E48" s="3">
+        <v>27800</v>
+      </c>
+      <c r="F48" s="3">
         <v>2500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1100</v>
-      </c>
-      <c r="G48" s="3">
-        <v>1400</v>
       </c>
       <c r="H48" s="3">
         <v>1400</v>
       </c>
       <c r="I48" s="3">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="J48" s="3">
         <v>1500</v>
       </c>
       <c r="K48" s="3">
+        <v>1500</v>
+      </c>
+      <c r="L48" s="3">
         <v>2000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1700</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3314,65 +3422,68 @@
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>100</v>
+      </c>
+      <c r="E49" s="3">
         <v>1700</v>
       </c>
-      <c r="E49" s="3">
-        <v>19000</v>
-      </c>
       <c r="F49" s="3">
-        <v>21200</v>
+        <v>19200</v>
       </c>
       <c r="G49" s="3">
-        <v>51600</v>
+        <v>21300</v>
       </c>
       <c r="H49" s="3">
-        <v>74800</v>
+        <v>51900</v>
       </c>
       <c r="I49" s="3">
-        <v>84600</v>
+        <v>75300</v>
       </c>
       <c r="J49" s="3">
+        <v>85200</v>
+      </c>
+      <c r="K49" s="3">
         <v>95600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>117800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>129200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>147300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>168300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>396000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>395600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>391000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>378700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>388200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>232000</v>
       </c>
-      <c r="U49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3385,8 +3496,11 @@
       <c r="Y49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3456,8 +3570,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3527,65 +3644,68 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E52" s="3">
         <v>8800</v>
       </c>
-      <c r="E52" s="3">
-        <v>32600</v>
-      </c>
       <c r="F52" s="3">
-        <v>29700</v>
+        <v>32900</v>
       </c>
       <c r="G52" s="3">
-        <v>29800</v>
+        <v>29900</v>
       </c>
       <c r="H52" s="3">
-        <v>22600</v>
+        <v>30000</v>
       </c>
       <c r="I52" s="3">
+        <v>22700</v>
+      </c>
+      <c r="J52" s="3">
+        <v>22700</v>
+      </c>
+      <c r="K52" s="3">
         <v>22500</v>
       </c>
-      <c r="J52" s="3">
-        <v>22500</v>
-      </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>17200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2700</v>
-      </c>
-      <c r="P52" s="3">
-        <v>100</v>
       </c>
       <c r="Q52" s="3">
         <v>100</v>
       </c>
       <c r="R52" s="3">
+        <v>100</v>
+      </c>
+      <c r="S52" s="3">
         <v>1300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1600</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3598,8 +3718,11 @@
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3669,65 +3792,68 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>136200</v>
+        <v>129000</v>
       </c>
       <c r="E54" s="3">
-        <v>155100</v>
+        <v>137100</v>
       </c>
       <c r="F54" s="3">
-        <v>161100</v>
+        <v>156200</v>
       </c>
       <c r="G54" s="3">
-        <v>198700</v>
+        <v>162200</v>
       </c>
       <c r="H54" s="3">
-        <v>238700</v>
+        <v>200000</v>
       </c>
       <c r="I54" s="3">
-        <v>254000</v>
+        <v>240300</v>
       </c>
       <c r="J54" s="3">
+        <v>255800</v>
+      </c>
+      <c r="K54" s="3">
         <v>274700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>296300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>323400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>359700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>419200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>660700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>704100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>700300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>691600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>630600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>497800</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3740,8 +3866,11 @@
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3767,8 +3896,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3794,65 +3924,66 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>900</v>
+      </c>
+      <c r="E57" s="3">
         <v>1100</v>
       </c>
-      <c r="E57" s="3">
-        <v>2100</v>
-      </c>
       <c r="F57" s="3">
+        <v>2200</v>
+      </c>
+      <c r="G57" s="3">
         <v>2500</v>
       </c>
-      <c r="G57" s="3">
-        <v>1400</v>
-      </c>
       <c r="H57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="I57" s="3">
         <v>2600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>6500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3700</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3865,23 +3996,26 @@
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
-        <v>0</v>
+      <c r="D58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>1600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1400</v>
       </c>
-      <c r="G58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3897,8 +4031,8 @@
       <c r="L58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
+      <c r="M58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
@@ -3936,65 +4070,68 @@
       <c r="Y58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>41800</v>
+        <v>39400</v>
       </c>
       <c r="E59" s="3">
-        <v>39200</v>
+        <v>42100</v>
       </c>
       <c r="F59" s="3">
-        <v>40600</v>
+        <v>39400</v>
       </c>
       <c r="G59" s="3">
-        <v>46500</v>
+        <v>40800</v>
       </c>
       <c r="H59" s="3">
-        <v>47800</v>
+        <v>46800</v>
       </c>
       <c r="I59" s="3">
-        <v>47700</v>
+        <v>48100</v>
       </c>
       <c r="J59" s="3">
+        <v>48000</v>
+      </c>
+      <c r="K59" s="3">
         <v>52600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>52500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>54000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>61600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>79300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>77300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>76600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>80800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>83400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>76400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>93500</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4007,65 +4144,68 @@
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>42900</v>
+        <v>40300</v>
       </c>
       <c r="E60" s="3">
-        <v>42900</v>
+        <v>43200</v>
       </c>
       <c r="F60" s="3">
-        <v>44400</v>
+        <v>43200</v>
       </c>
       <c r="G60" s="3">
-        <v>48000</v>
+        <v>44700</v>
       </c>
       <c r="H60" s="3">
-        <v>50300</v>
+        <v>48300</v>
       </c>
       <c r="I60" s="3">
-        <v>50400</v>
+        <v>50700</v>
       </c>
       <c r="J60" s="3">
+        <v>50800</v>
+      </c>
+      <c r="K60" s="3">
         <v>57100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>55300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>57000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>64100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>85800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>81300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>79800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>83500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>85800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>78700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>97200</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4078,8 +4218,11 @@
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4149,65 +4292,68 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>200</v>
+      </c>
+      <c r="E62" s="3">
         <v>600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>4100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>4200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>4300</v>
-      </c>
-      <c r="P62" s="3">
-        <v>1100</v>
       </c>
       <c r="Q62" s="3">
         <v>1100</v>
       </c>
       <c r="R62" s="3">
+        <v>1100</v>
+      </c>
+      <c r="S62" s="3">
         <v>1200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2800</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4220,8 +4366,11 @@
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4291,8 +4440,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4362,8 +4514,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4433,65 +4588,68 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>48200</v>
+        <v>44300</v>
       </c>
       <c r="E66" s="3">
-        <v>50600</v>
+        <v>48500</v>
       </c>
       <c r="F66" s="3">
-        <v>52100</v>
+        <v>50900</v>
       </c>
       <c r="G66" s="3">
-        <v>57600</v>
+        <v>52400</v>
       </c>
       <c r="H66" s="3">
-        <v>52800</v>
+        <v>58000</v>
       </c>
       <c r="I66" s="3">
         <v>53200</v>
       </c>
       <c r="J66" s="3">
+        <v>53500</v>
+      </c>
+      <c r="K66" s="3">
         <v>59900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>59400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>60300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>67800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>89900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>85700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>80900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>84600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>87000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>80800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>100000</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4504,8 +4662,11 @@
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4531,8 +4692,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4602,8 +4764,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4673,8 +4838,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4724,14 +4892,14 @@
         <v>0</v>
       </c>
       <c r="S70" s="3">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3">
         <v>1261300</v>
       </c>
-      <c r="T70" s="3">
+      <c r="U70" s="3">
         <v>1040100</v>
       </c>
-      <c r="U70" s="3">
-        <v>0</v>
-      </c>
       <c r="V70" s="3">
         <v>0</v>
       </c>
@@ -4744,8 +4912,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4815,65 +4986,68 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-1214100</v>
+        <v>-1227500</v>
       </c>
       <c r="E72" s="3">
-        <v>-1197400</v>
+        <v>-1222300</v>
       </c>
       <c r="F72" s="3">
-        <v>-1189500</v>
+        <v>-1205600</v>
       </c>
       <c r="G72" s="3">
-        <v>-1158000</v>
+        <v>-1197600</v>
       </c>
       <c r="H72" s="3">
-        <v>-1114300</v>
+        <v>-1165900</v>
       </c>
       <c r="I72" s="3">
-        <v>-1101100</v>
+        <v>-1121900</v>
       </c>
       <c r="J72" s="3">
+        <v>-1108600</v>
+      </c>
+      <c r="K72" s="3">
         <v>-1086100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1112900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1076800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1126800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1174900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-903900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-864900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-825000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-767100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-743400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-668400</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4886,8 +5060,11 @@
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4957,8 +5134,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5028,8 +5208,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5099,65 +5282,68 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>88000</v>
+        <v>84800</v>
       </c>
       <c r="E76" s="3">
-        <v>104500</v>
+        <v>88600</v>
       </c>
       <c r="F76" s="3">
-        <v>109000</v>
+        <v>105300</v>
       </c>
       <c r="G76" s="3">
-        <v>141100</v>
+        <v>109800</v>
       </c>
       <c r="H76" s="3">
-        <v>185900</v>
+        <v>142000</v>
       </c>
       <c r="I76" s="3">
-        <v>200900</v>
+        <v>187200</v>
       </c>
       <c r="J76" s="3">
+        <v>202300</v>
+      </c>
+      <c r="K76" s="3">
         <v>214800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>236900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>263100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>291800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>329300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>575000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>623300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>615700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>604600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-711600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-642200</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5170,8 +5356,11 @@
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5241,155 +5430,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45016</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44834</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44651</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44469</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44377</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44286</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44196</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44104</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44012</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>43921</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>43830</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>43738</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>43646</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43555</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43465</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43373</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43281</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43190</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43100</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43008</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>42916</v>
       </c>
-      <c r="Y80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-16600</v>
+        <v>-4900</v>
       </c>
       <c r="E81" s="3">
-        <v>-7900</v>
+        <v>-16800</v>
       </c>
       <c r="F81" s="3">
-        <v>-31200</v>
+        <v>-8000</v>
       </c>
       <c r="G81" s="3">
-        <v>-44000</v>
+        <v>-31400</v>
       </c>
       <c r="H81" s="3">
-        <v>-13200</v>
+        <v>-44300</v>
       </c>
       <c r="I81" s="3">
-        <v>-15000</v>
+        <v>-13300</v>
       </c>
       <c r="J81" s="3">
+        <v>-15100</v>
+      </c>
+      <c r="K81" s="3">
         <v>-5100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-13300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-12400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-20900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-255900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-50300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-18800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-21400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-26300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-65900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-43300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>3700</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W81" s="3">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X81" s="3">
         <v>-63300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-49600</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5415,8 +5613,9 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5462,32 +5661,35 @@
       <c r="Q83" s="3">
         <v>0</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S83" s="3">
+      <c r="R83" s="3">
+        <v>0</v>
+      </c>
+      <c r="S83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T83" s="3">
         <v>8500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>4500</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W83" s="3">
+      <c r="W83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X83" s="3">
         <v>18700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>18900</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5557,8 +5759,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5628,8 +5833,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5699,8 +5907,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5770,8 +5981,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5841,79 +6055,85 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="E89" s="3">
         <v>800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2200</v>
       </c>
-      <c r="F89" s="3">
-        <v>-5600</v>
-      </c>
       <c r="G89" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="H89" s="3">
         <v>-8600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1600</v>
       </c>
-      <c r="I89" s="3">
-        <v>-6900</v>
-      </c>
       <c r="J89" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="K89" s="3">
         <v>1700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-4500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-22800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-5900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-13800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-13800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>4200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-35800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-2500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-19700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-18600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>26100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-33900</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5939,8 +6159,9 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5986,32 +6207,35 @@
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S91" s="3">
-        <v>-200</v>
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T91" s="3">
         <v>-200</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
+      <c r="U91" s="3">
+        <v>-200</v>
       </c>
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W91" s="3">
-        <v>-300</v>
+      <c r="W91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X91" s="3">
         <v>-300</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Z91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6081,8 +6305,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6152,79 +6379,85 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E94" s="3">
         <v>4000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-4900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-4500</v>
       </c>
-      <c r="H94" s="3">
-        <v>11300</v>
-      </c>
       <c r="I94" s="3">
-        <v>-8300</v>
+        <v>11400</v>
       </c>
       <c r="J94" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="K94" s="3">
         <v>13000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-16600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>20900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>2000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-22900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-18600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>21400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-11400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-12800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-7900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>11800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>33600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>11500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-6800</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6250,8 +6483,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6321,8 +6555,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6392,8 +6629,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6463,8 +6703,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6534,217 +6777,229 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="J100" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="K100" s="3">
         <v>-1000</v>
       </c>
-      <c r="I100" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="J100" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-13800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-3500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>61800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1600</v>
-      </c>
-      <c r="T100" s="3">
-        <v>100</v>
       </c>
       <c r="U100" s="3">
         <v>100</v>
       </c>
       <c r="V100" s="3">
+        <v>100</v>
+      </c>
+      <c r="W100" s="3">
         <v>300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>200</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>500</v>
+      </c>
+      <c r="E101" s="3">
         <v>-300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-100</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>-400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1600</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
       <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
         <v>800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>2700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>2600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-2500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>3900</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>5200</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-4400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-2000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-2900</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y101" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="E102" s="3">
         <v>3200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-6300</v>
       </c>
-      <c r="F102" s="3">
-        <v>-9400</v>
-      </c>
       <c r="G102" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="H102" s="3">
         <v>-13200</v>
       </c>
-      <c r="H102" s="3">
-        <v>8300</v>
-      </c>
       <c r="I102" s="3">
-        <v>-16200</v>
+        <v>8400</v>
       </c>
       <c r="J102" s="3">
+        <v>-16300</v>
+      </c>
+      <c r="K102" s="3">
         <v>12100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-36400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-4000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-5100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-36900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-21700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>54400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-43200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-5000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-12100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>13400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>35100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-42800</v>
       </c>
-      <c r="Y102" s="3" t="s">
+      <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MOGU_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MOGU_QTR_FIN.xlsx
@@ -773,22 +773,22 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>11600</v>
+        <v>11500</v>
       </c>
       <c r="E8" s="3">
-        <v>16300</v>
+        <v>16200</v>
       </c>
       <c r="F8" s="3">
-        <v>16000</v>
+        <v>15900</v>
       </c>
       <c r="G8" s="3">
-        <v>23400</v>
+        <v>23200</v>
       </c>
       <c r="H8" s="3">
-        <v>10800</v>
+        <v>10700</v>
       </c>
       <c r="I8" s="3">
-        <v>12800</v>
+        <v>12700</v>
       </c>
       <c r="J8" s="3">
         <v>12600</v>
@@ -853,10 +853,10 @@
         <v>7500</v>
       </c>
       <c r="F9" s="3">
-        <v>8300</v>
+        <v>8200</v>
       </c>
       <c r="G9" s="3">
-        <v>10400</v>
+        <v>10300</v>
       </c>
       <c r="H9" s="3">
         <v>5800</v>
@@ -865,7 +865,7 @@
         <v>6000</v>
       </c>
       <c r="J9" s="3">
-        <v>5300</v>
+        <v>5200</v>
       </c>
       <c r="K9" s="3">
         <v>7000</v>
@@ -924,22 +924,22 @@
         <v>4700</v>
       </c>
       <c r="E10" s="3">
-        <v>8800</v>
+        <v>8700</v>
       </c>
       <c r="F10" s="3">
-        <v>7700</v>
+        <v>7600</v>
       </c>
       <c r="G10" s="3">
-        <v>13000</v>
+        <v>12900</v>
       </c>
       <c r="H10" s="3">
-        <v>5000</v>
+        <v>4900</v>
       </c>
       <c r="I10" s="3">
         <v>6700</v>
       </c>
       <c r="J10" s="3">
-        <v>7400</v>
+        <v>7300</v>
       </c>
       <c r="K10" s="3">
         <v>13200</v>
@@ -1035,7 +1035,7 @@
         <v>5200</v>
       </c>
       <c r="H12" s="3">
-        <v>3300</v>
+        <v>3200</v>
       </c>
       <c r="I12" s="3">
         <v>3000</v>
@@ -1174,7 +1174,7 @@
         <v>1400</v>
       </c>
       <c r="E14" s="3">
-        <v>11800</v>
+        <v>11700</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
@@ -1183,7 +1183,7 @@
         <v>6800</v>
       </c>
       <c r="H14" s="3">
-        <v>25900</v>
+        <v>25800</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
@@ -1248,22 +1248,22 @@
         <v>300</v>
       </c>
       <c r="E15" s="3">
-        <v>5600</v>
+        <v>5500</v>
       </c>
       <c r="F15" s="3">
         <v>2800</v>
       </c>
       <c r="G15" s="3">
-        <v>23400</v>
+        <v>23200</v>
       </c>
       <c r="H15" s="3">
-        <v>13300</v>
+        <v>13200</v>
       </c>
       <c r="I15" s="3">
-        <v>9000</v>
+        <v>8900</v>
       </c>
       <c r="J15" s="3">
-        <v>11400</v>
+        <v>11300</v>
       </c>
       <c r="K15" s="3">
         <v>15700</v>
@@ -1344,25 +1344,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>18800</v>
+        <v>18700</v>
       </c>
       <c r="E17" s="3">
-        <v>35700</v>
+        <v>35500</v>
       </c>
       <c r="F17" s="3">
-        <v>22600</v>
+        <v>22500</v>
       </c>
       <c r="G17" s="3">
-        <v>56800</v>
+        <v>56400</v>
       </c>
       <c r="H17" s="3">
-        <v>56900</v>
+        <v>56600</v>
       </c>
       <c r="I17" s="3">
-        <v>26400</v>
+        <v>26200</v>
       </c>
       <c r="J17" s="3">
-        <v>28000</v>
+        <v>27800</v>
       </c>
       <c r="K17" s="3">
         <v>37300</v>
@@ -1421,22 +1421,22 @@
         <v>-7200</v>
       </c>
       <c r="E18" s="3">
-        <v>-19400</v>
+        <v>-19300</v>
       </c>
       <c r="F18" s="3">
-        <v>-6700</v>
+        <v>-6600</v>
       </c>
       <c r="G18" s="3">
-        <v>-33400</v>
+        <v>-33200</v>
       </c>
       <c r="H18" s="3">
-        <v>-46200</v>
+        <v>-45900</v>
       </c>
       <c r="I18" s="3">
-        <v>-13600</v>
+        <v>-13500</v>
       </c>
       <c r="J18" s="3">
-        <v>-15300</v>
+        <v>-15200</v>
       </c>
       <c r="K18" s="3">
         <v>-17000</v>
@@ -1597,22 +1597,22 @@
         <v>-5300</v>
       </c>
       <c r="E21" s="3">
-        <v>-15200</v>
+        <v>-15100</v>
       </c>
       <c r="F21" s="3">
         <v>-5100</v>
       </c>
       <c r="G21" s="3">
-        <v>-23300</v>
+        <v>-23100</v>
       </c>
       <c r="H21" s="3">
-        <v>-40200</v>
+        <v>-39900</v>
       </c>
       <c r="I21" s="3">
         <v>-4100</v>
       </c>
       <c r="J21" s="3">
-        <v>-20100</v>
+        <v>-20000</v>
       </c>
       <c r="K21" s="3">
         <v>1800</v>
@@ -1742,25 +1742,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-6100</v>
+        <v>-6000</v>
       </c>
       <c r="E23" s="3">
-        <v>-18100</v>
+        <v>-18000</v>
       </c>
       <c r="F23" s="3">
-        <v>-8200</v>
+        <v>-8100</v>
       </c>
       <c r="G23" s="3">
-        <v>-33500</v>
+        <v>-33300</v>
       </c>
       <c r="H23" s="3">
-        <v>-44400</v>
+        <v>-44200</v>
       </c>
       <c r="I23" s="3">
-        <v>-13300</v>
+        <v>-13200</v>
       </c>
       <c r="J23" s="3">
-        <v>-15400</v>
+        <v>-15300</v>
       </c>
       <c r="K23" s="3">
         <v>-3800</v>
@@ -1967,22 +1967,22 @@
         <v>-5800</v>
       </c>
       <c r="E26" s="3">
-        <v>-18000</v>
+        <v>-17900</v>
       </c>
       <c r="F26" s="3">
         <v>-8000</v>
       </c>
       <c r="G26" s="3">
-        <v>-31700</v>
+        <v>-31500</v>
       </c>
       <c r="H26" s="3">
-        <v>-44200</v>
+        <v>-43900</v>
       </c>
       <c r="I26" s="3">
-        <v>-13300</v>
+        <v>-13200</v>
       </c>
       <c r="J26" s="3">
-        <v>-15100</v>
+        <v>-15000</v>
       </c>
       <c r="K26" s="3">
         <v>-5100</v>
@@ -2041,22 +2041,22 @@
         <v>-4900</v>
       </c>
       <c r="E27" s="3">
-        <v>-16800</v>
+        <v>-16700</v>
       </c>
       <c r="F27" s="3">
-        <v>-8000</v>
+        <v>-7900</v>
       </c>
       <c r="G27" s="3">
-        <v>-31400</v>
+        <v>-31200</v>
       </c>
       <c r="H27" s="3">
-        <v>-44300</v>
+        <v>-44000</v>
       </c>
       <c r="I27" s="3">
-        <v>-13300</v>
+        <v>-13200</v>
       </c>
       <c r="J27" s="3">
-        <v>-15100</v>
+        <v>-15000</v>
       </c>
       <c r="K27" s="3">
         <v>-5100</v>
@@ -2485,22 +2485,22 @@
         <v>-4900</v>
       </c>
       <c r="E33" s="3">
-        <v>-16800</v>
+        <v>-16700</v>
       </c>
       <c r="F33" s="3">
-        <v>-8000</v>
+        <v>-7900</v>
       </c>
       <c r="G33" s="3">
-        <v>-31400</v>
+        <v>-31200</v>
       </c>
       <c r="H33" s="3">
-        <v>-44300</v>
+        <v>-44000</v>
       </c>
       <c r="I33" s="3">
-        <v>-13300</v>
+        <v>-13200</v>
       </c>
       <c r="J33" s="3">
-        <v>-15100</v>
+        <v>-15000</v>
       </c>
       <c r="K33" s="3">
         <v>-5100</v>
@@ -2633,22 +2633,22 @@
         <v>-4900</v>
       </c>
       <c r="E35" s="3">
-        <v>-16800</v>
+        <v>-16700</v>
       </c>
       <c r="F35" s="3">
-        <v>-8000</v>
+        <v>-7900</v>
       </c>
       <c r="G35" s="3">
-        <v>-31400</v>
+        <v>-31200</v>
       </c>
       <c r="H35" s="3">
-        <v>-44300</v>
+        <v>-44000</v>
       </c>
       <c r="I35" s="3">
-        <v>-13300</v>
+        <v>-13200</v>
       </c>
       <c r="J35" s="3">
-        <v>-15100</v>
+        <v>-15000</v>
       </c>
       <c r="K35" s="3">
         <v>-5100</v>
@@ -2839,25 +2839,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>50900</v>
+        <v>50600</v>
       </c>
       <c r="E41" s="3">
-        <v>57900</v>
+        <v>57500</v>
       </c>
       <c r="F41" s="3">
-        <v>54600</v>
+        <v>54300</v>
       </c>
       <c r="G41" s="3">
-        <v>61000</v>
+        <v>60600</v>
       </c>
       <c r="H41" s="3">
-        <v>70500</v>
+        <v>70100</v>
       </c>
       <c r="I41" s="3">
-        <v>83700</v>
+        <v>83200</v>
       </c>
       <c r="J41" s="3">
-        <v>75400</v>
+        <v>74900</v>
       </c>
       <c r="K41" s="3">
         <v>91000</v>
@@ -2913,25 +2913,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>14400</v>
+        <v>14300</v>
       </c>
       <c r="E42" s="3">
-        <v>20300</v>
+        <v>20100</v>
       </c>
       <c r="F42" s="3">
-        <v>29300</v>
+        <v>29200</v>
       </c>
       <c r="G42" s="3">
-        <v>27400</v>
+        <v>27200</v>
       </c>
       <c r="H42" s="3">
-        <v>15100</v>
+        <v>15000</v>
       </c>
       <c r="I42" s="3">
-        <v>24100</v>
+        <v>23900</v>
       </c>
       <c r="J42" s="3">
-        <v>36200</v>
+        <v>36000</v>
       </c>
       <c r="K42" s="3">
         <v>22100</v>
@@ -2996,16 +2996,16 @@
         <v>1500</v>
       </c>
       <c r="G43" s="3">
-        <v>5100</v>
+        <v>5000</v>
       </c>
       <c r="H43" s="3">
-        <v>11600</v>
+        <v>11500</v>
       </c>
       <c r="I43" s="3">
-        <v>13700</v>
+        <v>13600</v>
       </c>
       <c r="J43" s="3">
-        <v>17700</v>
+        <v>17600</v>
       </c>
       <c r="K43" s="3">
         <v>19400</v>
@@ -3135,7 +3135,7 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>13900</v>
+        <v>13800</v>
       </c>
       <c r="E45" s="3">
         <v>9700</v>
@@ -3147,13 +3147,13 @@
         <v>6500</v>
       </c>
       <c r="H45" s="3">
-        <v>8600</v>
+        <v>8500</v>
       </c>
       <c r="I45" s="3">
-        <v>9200</v>
+        <v>9100</v>
       </c>
       <c r="J45" s="3">
-        <v>8000</v>
+        <v>7900</v>
       </c>
       <c r="K45" s="3">
         <v>13800</v>
@@ -3209,25 +3209,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>79800</v>
+        <v>79300</v>
       </c>
       <c r="E46" s="3">
-        <v>89100</v>
+        <v>88500</v>
       </c>
       <c r="F46" s="3">
-        <v>93100</v>
+        <v>92500</v>
       </c>
       <c r="G46" s="3">
-        <v>99900</v>
+        <v>99300</v>
       </c>
       <c r="H46" s="3">
-        <v>105700</v>
+        <v>105100</v>
       </c>
       <c r="I46" s="3">
-        <v>130700</v>
+        <v>129900</v>
       </c>
       <c r="J46" s="3">
-        <v>137200</v>
+        <v>136400</v>
       </c>
       <c r="K46" s="3">
         <v>146400</v>
@@ -3295,10 +3295,10 @@
         <v>10000</v>
       </c>
       <c r="H47" s="3">
-        <v>11000</v>
+        <v>10900</v>
       </c>
       <c r="I47" s="3">
-        <v>10200</v>
+        <v>10100</v>
       </c>
       <c r="J47" s="3">
         <v>9200</v>
@@ -3357,10 +3357,10 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>31200</v>
+        <v>31000</v>
       </c>
       <c r="E48" s="3">
-        <v>27800</v>
+        <v>27600</v>
       </c>
       <c r="F48" s="3">
         <v>2500</v>
@@ -3437,19 +3437,19 @@
         <v>1700</v>
       </c>
       <c r="F49" s="3">
-        <v>19200</v>
+        <v>19000</v>
       </c>
       <c r="G49" s="3">
-        <v>21300</v>
+        <v>21200</v>
       </c>
       <c r="H49" s="3">
-        <v>51900</v>
+        <v>51600</v>
       </c>
       <c r="I49" s="3">
-        <v>75300</v>
+        <v>74800</v>
       </c>
       <c r="J49" s="3">
-        <v>85200</v>
+        <v>84600</v>
       </c>
       <c r="K49" s="3">
         <v>95600</v>
@@ -3653,25 +3653,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>6500</v>
+        <v>6400</v>
       </c>
       <c r="E52" s="3">
         <v>8800</v>
       </c>
       <c r="F52" s="3">
-        <v>32900</v>
+        <v>32700</v>
       </c>
       <c r="G52" s="3">
-        <v>29900</v>
+        <v>29700</v>
       </c>
       <c r="H52" s="3">
-        <v>30000</v>
+        <v>29800</v>
       </c>
       <c r="I52" s="3">
-        <v>22700</v>
+        <v>22600</v>
       </c>
       <c r="J52" s="3">
-        <v>22700</v>
+        <v>22500</v>
       </c>
       <c r="K52" s="3">
         <v>22500</v>
@@ -3801,25 +3801,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>129000</v>
+        <v>128200</v>
       </c>
       <c r="E54" s="3">
-        <v>137100</v>
+        <v>136200</v>
       </c>
       <c r="F54" s="3">
-        <v>156200</v>
+        <v>155200</v>
       </c>
       <c r="G54" s="3">
-        <v>162200</v>
+        <v>161200</v>
       </c>
       <c r="H54" s="3">
-        <v>200000</v>
+        <v>198800</v>
       </c>
       <c r="I54" s="3">
-        <v>240300</v>
+        <v>238900</v>
       </c>
       <c r="J54" s="3">
-        <v>255800</v>
+        <v>254200</v>
       </c>
       <c r="K54" s="3">
         <v>274700</v>
@@ -3943,7 +3943,7 @@
         <v>2500</v>
       </c>
       <c r="H57" s="3">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="I57" s="3">
         <v>2600</v>
@@ -4079,25 +4079,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>39400</v>
+        <v>39200</v>
       </c>
       <c r="E59" s="3">
-        <v>42100</v>
+        <v>41800</v>
       </c>
       <c r="F59" s="3">
-        <v>39400</v>
+        <v>39200</v>
       </c>
       <c r="G59" s="3">
-        <v>40800</v>
+        <v>40600</v>
       </c>
       <c r="H59" s="3">
-        <v>46800</v>
+        <v>46500</v>
       </c>
       <c r="I59" s="3">
-        <v>48100</v>
+        <v>47800</v>
       </c>
       <c r="J59" s="3">
-        <v>48000</v>
+        <v>47700</v>
       </c>
       <c r="K59" s="3">
         <v>52600</v>
@@ -4153,25 +4153,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>40300</v>
+        <v>40100</v>
       </c>
       <c r="E60" s="3">
-        <v>43200</v>
+        <v>42900</v>
       </c>
       <c r="F60" s="3">
-        <v>43200</v>
+        <v>43000</v>
       </c>
       <c r="G60" s="3">
-        <v>44700</v>
+        <v>44500</v>
       </c>
       <c r="H60" s="3">
-        <v>48300</v>
+        <v>48000</v>
       </c>
       <c r="I60" s="3">
-        <v>50700</v>
+        <v>50300</v>
       </c>
       <c r="J60" s="3">
-        <v>50800</v>
+        <v>50500</v>
       </c>
       <c r="K60" s="3">
         <v>57100</v>
@@ -4597,25 +4597,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>44300</v>
+        <v>44000</v>
       </c>
       <c r="E66" s="3">
-        <v>48500</v>
+        <v>48200</v>
       </c>
       <c r="F66" s="3">
-        <v>50900</v>
+        <v>50600</v>
       </c>
       <c r="G66" s="3">
-        <v>52400</v>
+        <v>52100</v>
       </c>
       <c r="H66" s="3">
-        <v>58000</v>
+        <v>57600</v>
       </c>
       <c r="I66" s="3">
+        <v>52900</v>
+      </c>
+      <c r="J66" s="3">
         <v>53200</v>
-      </c>
-      <c r="J66" s="3">
-        <v>53500</v>
       </c>
       <c r="K66" s="3">
         <v>59900</v>
@@ -4995,25 +4995,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-1227500</v>
+        <v>-1219900</v>
       </c>
       <c r="E72" s="3">
-        <v>-1222300</v>
+        <v>-1214800</v>
       </c>
       <c r="F72" s="3">
-        <v>-1205600</v>
+        <v>-1198100</v>
       </c>
       <c r="G72" s="3">
-        <v>-1197600</v>
+        <v>-1190200</v>
       </c>
       <c r="H72" s="3">
-        <v>-1165900</v>
+        <v>-1158700</v>
       </c>
       <c r="I72" s="3">
-        <v>-1121900</v>
+        <v>-1115000</v>
       </c>
       <c r="J72" s="3">
-        <v>-1108600</v>
+        <v>-1101800</v>
       </c>
       <c r="K72" s="3">
         <v>-1086100</v>
@@ -5291,25 +5291,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>84800</v>
+        <v>84200</v>
       </c>
       <c r="E76" s="3">
-        <v>88600</v>
+        <v>88100</v>
       </c>
       <c r="F76" s="3">
-        <v>105300</v>
+        <v>104600</v>
       </c>
       <c r="G76" s="3">
-        <v>109800</v>
+        <v>109100</v>
       </c>
       <c r="H76" s="3">
-        <v>142000</v>
+        <v>141200</v>
       </c>
       <c r="I76" s="3">
-        <v>187200</v>
+        <v>186000</v>
       </c>
       <c r="J76" s="3">
-        <v>202300</v>
+        <v>201000</v>
       </c>
       <c r="K76" s="3">
         <v>214800</v>
@@ -5521,22 +5521,22 @@
         <v>-4900</v>
       </c>
       <c r="E81" s="3">
-        <v>-16800</v>
+        <v>-16700</v>
       </c>
       <c r="F81" s="3">
-        <v>-8000</v>
+        <v>-7900</v>
       </c>
       <c r="G81" s="3">
-        <v>-31400</v>
+        <v>-31200</v>
       </c>
       <c r="H81" s="3">
-        <v>-44300</v>
+        <v>-44000</v>
       </c>
       <c r="I81" s="3">
-        <v>-13300</v>
+        <v>-13200</v>
       </c>
       <c r="J81" s="3">
-        <v>-15100</v>
+        <v>-15000</v>
       </c>
       <c r="K81" s="3">
         <v>-5100</v>
@@ -6064,7 +6064,7 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-4600</v>
+        <v>-4500</v>
       </c>
       <c r="E89" s="3">
         <v>800</v>
@@ -6073,7 +6073,7 @@
         <v>-2200</v>
       </c>
       <c r="G89" s="3">
-        <v>-5700</v>
+        <v>-5600</v>
       </c>
       <c r="H89" s="3">
         <v>-8600</v>
@@ -6082,7 +6082,7 @@
         <v>-1600</v>
       </c>
       <c r="J89" s="3">
-        <v>-7000</v>
+        <v>-6900</v>
       </c>
       <c r="K89" s="3">
         <v>1700</v>
@@ -6403,10 +6403,10 @@
         <v>-4500</v>
       </c>
       <c r="I94" s="3">
-        <v>11400</v>
+        <v>11300</v>
       </c>
       <c r="J94" s="3">
-        <v>-8400</v>
+        <v>-8300</v>
       </c>
       <c r="K94" s="3">
         <v>13000</v>
@@ -6801,7 +6801,7 @@
         <v>-100</v>
       </c>
       <c r="I100" s="3">
-        <v>-1100</v>
+        <v>-1000</v>
       </c>
       <c r="J100" s="3">
         <v>-1300</v>
@@ -6949,10 +6949,10 @@
         <v>-13200</v>
       </c>
       <c r="I102" s="3">
-        <v>8400</v>
+        <v>8300</v>
       </c>
       <c r="J102" s="3">
-        <v>-16300</v>
+        <v>-16200</v>
       </c>
       <c r="K102" s="3">
         <v>12100</v>

--- a/AAII_Financials/Quarterly/MOGU_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MOGU_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="92">
   <si>
     <t>MOGU</t>
   </si>
@@ -656,341 +656,354 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44834</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44651</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44469</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44377</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44286</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44196</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44104</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44012</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>43921</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>43830</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>43738</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43646</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43555</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43465</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43373</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43281</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43190</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43100</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43008</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>42916</v>
       </c>
-      <c r="Z7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>11500</v>
+        <v>10900</v>
       </c>
       <c r="E8" s="3">
+        <v>11700</v>
+      </c>
+      <c r="F8" s="3">
+        <v>16500</v>
+      </c>
+      <c r="G8" s="3">
         <v>16200</v>
       </c>
-      <c r="F8" s="3">
-        <v>15900</v>
-      </c>
-      <c r="G8" s="3">
-        <v>23200</v>
-      </c>
       <c r="H8" s="3">
-        <v>10700</v>
+        <v>23700</v>
       </c>
       <c r="I8" s="3">
-        <v>12700</v>
+        <v>10900</v>
       </c>
       <c r="J8" s="3">
+        <v>13000</v>
+      </c>
+      <c r="K8" s="3">
         <v>12600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>20200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>16000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>18400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>17500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>42200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>30500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>38800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>33100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>53300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>33900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>35800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>26900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>45300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>32000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>39300</v>
       </c>
-      <c r="Z8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>6900</v>
+        <v>5900</v>
       </c>
       <c r="E9" s="3">
-        <v>7500</v>
+        <v>7000</v>
       </c>
       <c r="F9" s="3">
-        <v>8200</v>
+        <v>7600</v>
       </c>
       <c r="G9" s="3">
+        <v>8400</v>
+      </c>
+      <c r="H9" s="3">
+        <v>10500</v>
+      </c>
+      <c r="I9" s="3">
+        <v>5900</v>
+      </c>
+      <c r="J9" s="3">
+        <v>6100</v>
+      </c>
+      <c r="K9" s="3">
+        <v>5200</v>
+      </c>
+      <c r="L9" s="3">
+        <v>7000</v>
+      </c>
+      <c r="M9" s="3">
+        <v>6500</v>
+      </c>
+      <c r="N9" s="3">
+        <v>6800</v>
+      </c>
+      <c r="O9" s="3">
+        <v>8600</v>
+      </c>
+      <c r="P9" s="3">
+        <v>15400</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>11700</v>
+      </c>
+      <c r="R9" s="3">
+        <v>9500</v>
+      </c>
+      <c r="S9" s="3">
+        <v>9300</v>
+      </c>
+      <c r="T9" s="3">
+        <v>14600</v>
+      </c>
+      <c r="U9" s="3">
+        <v>11500</v>
+      </c>
+      <c r="V9" s="3">
         <v>10300</v>
       </c>
-      <c r="H9" s="3">
-        <v>5800</v>
-      </c>
-      <c r="I9" s="3">
-        <v>6000</v>
-      </c>
-      <c r="J9" s="3">
-        <v>5200</v>
-      </c>
-      <c r="K9" s="3">
-        <v>7000</v>
-      </c>
-      <c r="L9" s="3">
-        <v>6500</v>
-      </c>
-      <c r="M9" s="3">
-        <v>6800</v>
-      </c>
-      <c r="N9" s="3">
-        <v>8600</v>
-      </c>
-      <c r="O9" s="3">
-        <v>15400</v>
-      </c>
-      <c r="P9" s="3">
-        <v>11700</v>
-      </c>
-      <c r="Q9" s="3">
-        <v>9500</v>
-      </c>
-      <c r="R9" s="3">
-        <v>9300</v>
-      </c>
-      <c r="S9" s="3">
-        <v>14600</v>
-      </c>
-      <c r="T9" s="3">
-        <v>11500</v>
-      </c>
-      <c r="U9" s="3">
-        <v>10300</v>
-      </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>10900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>12300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>11600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>12000</v>
       </c>
-      <c r="Z9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>4700</v>
+        <v>5000</v>
       </c>
       <c r="E10" s="3">
-        <v>8700</v>
+        <v>4800</v>
       </c>
       <c r="F10" s="3">
-        <v>7600</v>
+        <v>8900</v>
       </c>
       <c r="G10" s="3">
-        <v>12900</v>
+        <v>7800</v>
       </c>
       <c r="H10" s="3">
-        <v>4900</v>
+        <v>13200</v>
       </c>
       <c r="I10" s="3">
-        <v>6700</v>
+        <v>5100</v>
       </c>
       <c r="J10" s="3">
+        <v>6800</v>
+      </c>
+      <c r="K10" s="3">
         <v>7300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>13200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>9500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>11700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>8900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>26800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>18800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>29400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>23800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>38700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>22500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>25600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>16000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>33000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>20400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>27300</v>
       </c>
-      <c r="Z10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1017,82 +1030,86 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>1900</v>
+        <v>1800</v>
       </c>
       <c r="E12" s="3">
-        <v>2200</v>
+        <v>2000</v>
       </c>
       <c r="F12" s="3">
+        <v>2300</v>
+      </c>
+      <c r="G12" s="3">
         <v>2900</v>
       </c>
-      <c r="G12" s="3">
-        <v>5200</v>
-      </c>
       <c r="H12" s="3">
-        <v>3200</v>
+        <v>5300</v>
       </c>
       <c r="I12" s="3">
-        <v>3000</v>
+        <v>3300</v>
       </c>
       <c r="J12" s="3">
+        <v>3100</v>
+      </c>
+      <c r="K12" s="3">
         <v>2700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>3800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>3900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>4000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>4800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>5000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>7700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>8800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>8700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>8000</v>
-      </c>
-      <c r="T12" s="3">
-        <v>8800</v>
       </c>
       <c r="U12" s="3">
         <v>8800</v>
       </c>
       <c r="V12" s="3">
+        <v>8800</v>
+      </c>
+      <c r="W12" s="3">
         <v>10000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>10500</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>11300</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>10800</v>
       </c>
-      <c r="Z12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1165,28 +1182,31 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>1400</v>
       </c>
-      <c r="E14" s="3">
-        <v>11700</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3">
-        <v>6800</v>
+      <c r="F14" s="3">
+        <v>11900</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H14" s="3">
-        <v>25800</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
+        <v>6900</v>
+      </c>
+      <c r="I14" s="3">
+        <v>26300</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
@@ -1200,20 +1220,20 @@
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>216400</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="R14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
@@ -1221,88 +1241,91 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>-2000</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3" t="s">
-        <v>3</v>
+      <c r="Y14" s="3">
+        <v>0</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
         <v>300</v>
       </c>
-      <c r="E15" s="3">
-        <v>5500</v>
-      </c>
       <c r="F15" s="3">
+        <v>5600</v>
+      </c>
+      <c r="G15" s="3">
         <v>2800</v>
       </c>
-      <c r="G15" s="3">
-        <v>23200</v>
-      </c>
       <c r="H15" s="3">
-        <v>13200</v>
+        <v>23700</v>
       </c>
       <c r="I15" s="3">
-        <v>8900</v>
+        <v>13500</v>
       </c>
       <c r="J15" s="3">
+        <v>9100</v>
+      </c>
+      <c r="K15" s="3">
         <v>11300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>15700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>10800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>9800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>12800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>16100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>11800</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>10100</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>6800</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>9700</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>8000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>3900</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>7900</v>
-      </c>
-      <c r="W15" s="3">
-        <v>16300</v>
       </c>
       <c r="X15" s="3">
         <v>16300</v>
@@ -1310,11 +1333,14 @@
       <c r="Y15" s="3">
         <v>16300</v>
       </c>
-      <c r="Z15" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>16300</v>
+      </c>
+      <c r="AA15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1338,156 +1364,163 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>18700</v>
+        <v>14700</v>
       </c>
       <c r="E17" s="3">
-        <v>35500</v>
+        <v>19100</v>
       </c>
       <c r="F17" s="3">
-        <v>22500</v>
+        <v>36200</v>
       </c>
       <c r="G17" s="3">
-        <v>56400</v>
+        <v>23000</v>
       </c>
       <c r="H17" s="3">
-        <v>56600</v>
+        <v>57600</v>
       </c>
       <c r="I17" s="3">
-        <v>26200</v>
+        <v>57800</v>
       </c>
       <c r="J17" s="3">
+        <v>26800</v>
+      </c>
+      <c r="K17" s="3">
         <v>27800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>37300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>30300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>31700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>39500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>291900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>64900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>55300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>58700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>67500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>61800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>52100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>47900</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X17" s="3">
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y17" s="3">
         <v>76000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>69400</v>
       </c>
-      <c r="Z17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-7200</v>
+        <v>-3800</v>
       </c>
       <c r="E18" s="3">
-        <v>-19300</v>
+        <v>-7300</v>
       </c>
       <c r="F18" s="3">
-        <v>-6600</v>
+        <v>-19700</v>
       </c>
       <c r="G18" s="3">
-        <v>-33200</v>
+        <v>-6800</v>
       </c>
       <c r="H18" s="3">
-        <v>-45900</v>
+        <v>-33900</v>
       </c>
       <c r="I18" s="3">
-        <v>-13500</v>
+        <v>-46800</v>
       </c>
       <c r="J18" s="3">
+        <v>-13800</v>
+      </c>
+      <c r="K18" s="3">
         <v>-15200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-17000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-14300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-13200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-22000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-249700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-34400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-16400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-25600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-14200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-27900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-16300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-20900</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X18" s="3">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y18" s="3">
         <v>-44000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-30100</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1514,156 +1547,163 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>1200</v>
+        <v>700</v>
       </c>
       <c r="E20" s="3">
         <v>1200</v>
       </c>
       <c r="F20" s="3">
+        <v>1300</v>
+      </c>
+      <c r="G20" s="3">
         <v>-1500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-100</v>
       </c>
-      <c r="H20" s="3">
-        <v>1700</v>
-      </c>
       <c r="I20" s="3">
+        <v>1800</v>
+      </c>
+      <c r="J20" s="3">
         <v>300</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>13300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-4100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>5700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>23700</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X20" s="3">
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y20" s="3">
         <v>1900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>900</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-5300</v>
+        <v>-2500</v>
       </c>
       <c r="E21" s="3">
-        <v>-15100</v>
+        <v>-5400</v>
       </c>
       <c r="F21" s="3">
-        <v>-5100</v>
+        <v>-15400</v>
       </c>
       <c r="G21" s="3">
-        <v>-23100</v>
+        <v>-5200</v>
       </c>
       <c r="H21" s="3">
-        <v>-39900</v>
+        <v>-23600</v>
       </c>
       <c r="I21" s="3">
-        <v>-4100</v>
+        <v>-40700</v>
       </c>
       <c r="J21" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="K21" s="3">
         <v>-20000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-12700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-2500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-23400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-249700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-36400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-4800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-3300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-11600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-18100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-10700</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X21" s="3">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y21" s="3">
         <v>-23300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-10300</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1736,111 +1776,117 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-6000</v>
+        <v>-3100</v>
       </c>
       <c r="E23" s="3">
-        <v>-18000</v>
+        <v>-6200</v>
       </c>
       <c r="F23" s="3">
-        <v>-8100</v>
+        <v>-18400</v>
       </c>
       <c r="G23" s="3">
-        <v>-33300</v>
+        <v>-8300</v>
       </c>
       <c r="H23" s="3">
-        <v>-44200</v>
+        <v>-34000</v>
       </c>
       <c r="I23" s="3">
-        <v>-13200</v>
+        <v>-45100</v>
       </c>
       <c r="J23" s="3">
+        <v>-13500</v>
+      </c>
+      <c r="K23" s="3">
         <v>-15300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-3800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-13500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-12500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-21100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-253800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-38300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-15100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-24200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-8500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-26600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-15200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-26800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-42100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-29200</v>
       </c>
-      <c r="Z23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
         <v>-200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-1800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-200</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
         <v>-300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1300</v>
-      </c>
-      <c r="L24" s="3">
-        <v>-200</v>
       </c>
       <c r="M24" s="3">
         <v>-200</v>
@@ -1849,43 +1895,46 @@
         <v>-200</v>
       </c>
       <c r="O24" s="3">
+        <v>-200</v>
+      </c>
+      <c r="P24" s="3">
         <v>100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-1700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-3700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-3800</v>
       </c>
-      <c r="Z24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1958,156 +2007,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-5800</v>
+        <v>-3100</v>
       </c>
       <c r="E26" s="3">
-        <v>-17900</v>
+        <v>-5900</v>
       </c>
       <c r="F26" s="3">
-        <v>-8000</v>
+        <v>-18300</v>
       </c>
       <c r="G26" s="3">
-        <v>-31500</v>
+        <v>-8100</v>
       </c>
       <c r="H26" s="3">
-        <v>-43900</v>
+        <v>-32200</v>
       </c>
       <c r="I26" s="3">
-        <v>-13200</v>
+        <v>-44800</v>
       </c>
       <c r="J26" s="3">
+        <v>-13500</v>
+      </c>
+      <c r="K26" s="3">
         <v>-15000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-5100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-13300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-12400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-20900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-254000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-38200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-15200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-23400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-8300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-25800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-14500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>4400</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X26" s="3">
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y26" s="3">
         <v>-38200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-25300</v>
       </c>
-      <c r="Z26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-4900</v>
+        <v>-3400</v>
       </c>
       <c r="E27" s="3">
-        <v>-16700</v>
+        <v>-5000</v>
       </c>
       <c r="F27" s="3">
-        <v>-7900</v>
+        <v>-17000</v>
       </c>
       <c r="G27" s="3">
-        <v>-31200</v>
+        <v>-8100</v>
       </c>
       <c r="H27" s="3">
-        <v>-44000</v>
+        <v>-31800</v>
       </c>
       <c r="I27" s="3">
-        <v>-13200</v>
+        <v>-44900</v>
       </c>
       <c r="J27" s="3">
+        <v>-13500</v>
+      </c>
+      <c r="K27" s="3">
         <v>-15000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-5100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-13300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-12400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-20900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-255900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-50300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-18800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-21400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-26300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-65900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-43300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>3700</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X27" s="3">
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y27" s="3">
         <v>-63300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-49600</v>
       </c>
-      <c r="Z27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2180,8 +2238,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2254,8 +2315,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2328,8 +2392,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2402,156 +2469,165 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-1200</v>
+        <v>-700</v>
       </c>
       <c r="E32" s="3">
         <v>-1200</v>
       </c>
       <c r="F32" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="G32" s="3">
         <v>1500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>100</v>
       </c>
-      <c r="H32" s="3">
-        <v>-1700</v>
-      </c>
       <c r="I32" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="J32" s="3">
         <v>-300</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-13300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>4100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>3900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-5700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-23700</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X32" s="3">
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-900</v>
       </c>
-      <c r="Z32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-4900</v>
+        <v>-3400</v>
       </c>
       <c r="E33" s="3">
-        <v>-16700</v>
+        <v>-5000</v>
       </c>
       <c r="F33" s="3">
-        <v>-7900</v>
+        <v>-17000</v>
       </c>
       <c r="G33" s="3">
-        <v>-31200</v>
+        <v>-8100</v>
       </c>
       <c r="H33" s="3">
-        <v>-44000</v>
+        <v>-31800</v>
       </c>
       <c r="I33" s="3">
-        <v>-13200</v>
+        <v>-44900</v>
       </c>
       <c r="J33" s="3">
+        <v>-13500</v>
+      </c>
+      <c r="K33" s="3">
         <v>-15000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-5100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-13300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-12400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-20900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-255900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-50300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-18800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-21400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-26300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-65900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-43300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>3700</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X33" s="3">
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y33" s="3">
         <v>-63300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-49600</v>
       </c>
-      <c r="Z33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2624,161 +2700,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-4900</v>
+        <v>-3400</v>
       </c>
       <c r="E35" s="3">
-        <v>-16700</v>
+        <v>-5000</v>
       </c>
       <c r="F35" s="3">
-        <v>-7900</v>
+        <v>-17000</v>
       </c>
       <c r="G35" s="3">
-        <v>-31200</v>
+        <v>-8100</v>
       </c>
       <c r="H35" s="3">
-        <v>-44000</v>
+        <v>-31800</v>
       </c>
       <c r="I35" s="3">
-        <v>-13200</v>
+        <v>-44900</v>
       </c>
       <c r="J35" s="3">
+        <v>-13500</v>
+      </c>
+      <c r="K35" s="3">
         <v>-15000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-5100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-13300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-12400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-20900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-255900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-50300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-18800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-21400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-26300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-65900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-43300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>3700</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X35" s="3">
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y35" s="3">
         <v>-63300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-49600</v>
       </c>
-      <c r="Z35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44834</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44651</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44469</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44377</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44286</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44196</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44104</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44012</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>43921</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>43830</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>43738</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43646</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43555</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43465</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43373</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43281</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43190</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43100</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43008</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>42916</v>
       </c>
-      <c r="Z38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2805,8 +2890,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2833,8 +2919,9 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -2842,59 +2929,59 @@
         <v>50600</v>
       </c>
       <c r="E41" s="3">
-        <v>57500</v>
+        <v>51600</v>
       </c>
       <c r="F41" s="3">
-        <v>54300</v>
+        <v>58700</v>
       </c>
       <c r="G41" s="3">
-        <v>60600</v>
+        <v>55400</v>
       </c>
       <c r="H41" s="3">
-        <v>70100</v>
+        <v>61800</v>
       </c>
       <c r="I41" s="3">
-        <v>83200</v>
+        <v>71500</v>
       </c>
       <c r="J41" s="3">
+        <v>84900</v>
+      </c>
+      <c r="K41" s="3">
         <v>74900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>91000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>81300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>115200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>126200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>135500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>138300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>177500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>194200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>183900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>129500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>166400</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2907,68 +2994,71 @@
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>14300</v>
+        <v>8600</v>
       </c>
       <c r="E42" s="3">
-        <v>20100</v>
+        <v>14600</v>
       </c>
       <c r="F42" s="3">
-        <v>29200</v>
+        <v>20600</v>
       </c>
       <c r="G42" s="3">
-        <v>27200</v>
+        <v>29800</v>
       </c>
       <c r="H42" s="3">
-        <v>15000</v>
+        <v>27800</v>
       </c>
       <c r="I42" s="3">
-        <v>23900</v>
+        <v>15300</v>
       </c>
       <c r="J42" s="3">
+        <v>24400</v>
+      </c>
+      <c r="K42" s="3">
         <v>36000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>22100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>32700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>30600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>35100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>50900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>59900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>50500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>32200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>50400</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>44400</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>32200</v>
       </c>
-      <c r="V42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2981,68 +3071,71 @@
       <c r="Z42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E43" s="3">
         <v>600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1500</v>
       </c>
-      <c r="G43" s="3">
-        <v>5000</v>
-      </c>
       <c r="H43" s="3">
-        <v>11500</v>
+        <v>5100</v>
       </c>
       <c r="I43" s="3">
-        <v>13600</v>
+        <v>11700</v>
       </c>
       <c r="J43" s="3">
+        <v>13900</v>
+      </c>
+      <c r="K43" s="3">
         <v>17600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>19400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>16100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>16500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>16700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>27900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>21600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>18900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>18700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>19200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>27400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>30000</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3055,8 +3148,11 @@
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3082,40 +3178,40 @@
         <v>0</v>
       </c>
       <c r="K44" s="3">
+        <v>0</v>
+      </c>
+      <c r="L44" s="3">
         <v>100</v>
-      </c>
-      <c r="L44" s="3">
-        <v>300</v>
       </c>
       <c r="M44" s="3">
         <v>300</v>
       </c>
       <c r="N44" s="3">
+        <v>300</v>
+      </c>
+      <c r="O44" s="3">
         <v>400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>500</v>
-      </c>
-      <c r="Q44" s="3">
-        <v>800</v>
       </c>
       <c r="R44" s="3">
         <v>800</v>
       </c>
       <c r="S44" s="3">
+        <v>800</v>
+      </c>
+      <c r="T44" s="3">
         <v>700</v>
-      </c>
-      <c r="T44" s="3">
-        <v>100</v>
       </c>
       <c r="U44" s="3">
         <v>100</v>
       </c>
-      <c r="V44" s="3" t="s">
-        <v>3</v>
+      <c r="V44" s="3">
+        <v>100</v>
       </c>
       <c r="W44" s="3" t="s">
         <v>3</v>
@@ -3129,68 +3225,71 @@
       <c r="Z44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E45" s="3">
+        <v>14000</v>
+      </c>
+      <c r="F45" s="3">
+        <v>9900</v>
+      </c>
+      <c r="G45" s="3">
+        <v>7700</v>
+      </c>
+      <c r="H45" s="3">
+        <v>6600</v>
+      </c>
+      <c r="I45" s="3">
+        <v>8700</v>
+      </c>
+      <c r="J45" s="3">
+        <v>9300</v>
+      </c>
+      <c r="K45" s="3">
+        <v>7900</v>
+      </c>
+      <c r="L45" s="3">
         <v>13800</v>
-      </c>
-      <c r="E45" s="3">
-        <v>9700</v>
-      </c>
-      <c r="F45" s="3">
-        <v>7600</v>
-      </c>
-      <c r="G45" s="3">
-        <v>6500</v>
-      </c>
-      <c r="H45" s="3">
-        <v>8500</v>
-      </c>
-      <c r="I45" s="3">
-        <v>9100</v>
-      </c>
-      <c r="J45" s="3">
-        <v>7900</v>
-      </c>
-      <c r="K45" s="3">
-        <v>13800</v>
-      </c>
-      <c r="L45" s="3">
-        <v>11800</v>
       </c>
       <c r="M45" s="3">
         <v>11800</v>
       </c>
       <c r="N45" s="3">
+        <v>11800</v>
+      </c>
+      <c r="O45" s="3">
         <v>14700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>18600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>22100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>24400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>24700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>23900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>7300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>6300</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3203,68 +3302,71 @@
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>79300</v>
+        <v>71600</v>
       </c>
       <c r="E46" s="3">
-        <v>88500</v>
+        <v>80900</v>
       </c>
       <c r="F46" s="3">
-        <v>92500</v>
+        <v>90300</v>
       </c>
       <c r="G46" s="3">
-        <v>99300</v>
+        <v>94400</v>
       </c>
       <c r="H46" s="3">
-        <v>105100</v>
+        <v>101400</v>
       </c>
       <c r="I46" s="3">
-        <v>129900</v>
+        <v>107200</v>
       </c>
       <c r="J46" s="3">
+        <v>132500</v>
+      </c>
+      <c r="K46" s="3">
         <v>136400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>146400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>142100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>174500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>193100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>235000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>242400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>272100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>270600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>278000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>208700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>234900</v>
       </c>
-      <c r="V46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3277,68 +3379,71 @@
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>11400</v>
+        <v>11500</v>
       </c>
       <c r="E47" s="3">
-        <v>9600</v>
+        <v>11600</v>
       </c>
       <c r="F47" s="3">
-        <v>8500</v>
+        <v>9800</v>
       </c>
       <c r="G47" s="3">
-        <v>10000</v>
+        <v>8700</v>
       </c>
       <c r="H47" s="3">
-        <v>10900</v>
+        <v>10200</v>
       </c>
       <c r="I47" s="3">
-        <v>10100</v>
+        <v>11200</v>
       </c>
       <c r="J47" s="3">
+        <v>10300</v>
+      </c>
+      <c r="K47" s="3">
         <v>9200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>8600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>17200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>15900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>15100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>11300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>17300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>34200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>36800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>32000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>29200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>27600</v>
       </c>
-      <c r="V47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3351,25 +3456,28 @@
       <c r="Z47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>31000</v>
+        <v>42600</v>
       </c>
       <c r="E48" s="3">
-        <v>27600</v>
+        <v>31600</v>
       </c>
       <c r="F48" s="3">
-        <v>2500</v>
+        <v>28200</v>
       </c>
       <c r="G48" s="3">
+        <v>2600</v>
+      </c>
+      <c r="H48" s="3">
         <v>1100</v>
-      </c>
-      <c r="H48" s="3">
-        <v>1400</v>
       </c>
       <c r="I48" s="3">
         <v>1400</v>
@@ -3381,38 +3489,38 @@
         <v>1500</v>
       </c>
       <c r="L48" s="3">
+        <v>1500</v>
+      </c>
+      <c r="M48" s="3">
         <v>2000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1700</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3425,8 +3533,11 @@
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3434,59 +3545,59 @@
         <v>100</v>
       </c>
       <c r="E49" s="3">
-        <v>1700</v>
+        <v>100</v>
       </c>
       <c r="F49" s="3">
-        <v>19000</v>
+        <v>1800</v>
       </c>
       <c r="G49" s="3">
-        <v>21200</v>
+        <v>19400</v>
       </c>
       <c r="H49" s="3">
-        <v>51600</v>
+        <v>21600</v>
       </c>
       <c r="I49" s="3">
-        <v>74800</v>
+        <v>52700</v>
       </c>
       <c r="J49" s="3">
+        <v>76400</v>
+      </c>
+      <c r="K49" s="3">
         <v>84600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>95600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>117800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>129200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>147300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>168300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>396000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>395600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>391000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>378700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>388200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>232000</v>
       </c>
-      <c r="V49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3499,8 +3610,11 @@
       <c r="Z49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3573,8 +3687,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3647,8 +3764,11 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3656,59 +3776,59 @@
         <v>6400</v>
       </c>
       <c r="E52" s="3">
-        <v>8800</v>
+        <v>6500</v>
       </c>
       <c r="F52" s="3">
-        <v>32700</v>
+        <v>9000</v>
       </c>
       <c r="G52" s="3">
-        <v>29700</v>
+        <v>33300</v>
       </c>
       <c r="H52" s="3">
-        <v>29800</v>
+        <v>30300</v>
       </c>
       <c r="I52" s="3">
-        <v>22600</v>
+        <v>30400</v>
       </c>
       <c r="J52" s="3">
-        <v>22500</v>
+        <v>23100</v>
       </c>
       <c r="K52" s="3">
         <v>22500</v>
       </c>
       <c r="L52" s="3">
+        <v>22500</v>
+      </c>
+      <c r="M52" s="3">
         <v>17200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2700</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>100</v>
       </c>
       <c r="R52" s="3">
         <v>100</v>
       </c>
       <c r="S52" s="3">
+        <v>100</v>
+      </c>
+      <c r="T52" s="3">
         <v>1300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1600</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3721,8 +3841,11 @@
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3795,68 +3918,71 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>128200</v>
+        <v>132300</v>
       </c>
       <c r="E54" s="3">
-        <v>136200</v>
+        <v>130900</v>
       </c>
       <c r="F54" s="3">
-        <v>155200</v>
+        <v>139000</v>
       </c>
       <c r="G54" s="3">
-        <v>161200</v>
+        <v>158400</v>
       </c>
       <c r="H54" s="3">
-        <v>198800</v>
+        <v>164500</v>
       </c>
       <c r="I54" s="3">
-        <v>238900</v>
+        <v>202800</v>
       </c>
       <c r="J54" s="3">
+        <v>243700</v>
+      </c>
+      <c r="K54" s="3">
         <v>254200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>274700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>296300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>323400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>359700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>419200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>660700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>704100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>700300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>691600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>630600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>497800</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3869,8 +3995,11 @@
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3897,8 +4026,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3925,68 +4055,69 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E57" s="3">
         <v>900</v>
       </c>
-      <c r="E57" s="3">
-        <v>1100</v>
-      </c>
       <c r="F57" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G57" s="3">
         <v>2200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2500</v>
       </c>
-      <c r="H57" s="3">
-        <v>1400</v>
-      </c>
       <c r="I57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J57" s="3">
         <v>2600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>6500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3700</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3999,26 +4130,29 @@
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E58" s="3">
-        <v>0</v>
+      <c r="E58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F58" s="3">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3">
         <v>1600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1400</v>
       </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4034,8 +4168,8 @@
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
+      <c r="N58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O58" s="3">
         <v>0</v>
@@ -4073,68 +4207,71 @@
       <c r="Z58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>39200</v>
+        <v>44400</v>
       </c>
       <c r="E59" s="3">
-        <v>41800</v>
+        <v>40000</v>
       </c>
       <c r="F59" s="3">
-        <v>39200</v>
+        <v>42600</v>
       </c>
       <c r="G59" s="3">
-        <v>40600</v>
+        <v>40000</v>
       </c>
       <c r="H59" s="3">
-        <v>46500</v>
+        <v>41400</v>
       </c>
       <c r="I59" s="3">
-        <v>47800</v>
+        <v>47500</v>
       </c>
       <c r="J59" s="3">
+        <v>48800</v>
+      </c>
+      <c r="K59" s="3">
         <v>47700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>52600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>52500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>54000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>61600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>79300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>77300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>76600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>80800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>83400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>76400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>93500</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4147,68 +4284,71 @@
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>40100</v>
+        <v>45400</v>
       </c>
       <c r="E60" s="3">
-        <v>42900</v>
+        <v>40900</v>
       </c>
       <c r="F60" s="3">
-        <v>43000</v>
+        <v>43800</v>
       </c>
       <c r="G60" s="3">
-        <v>44500</v>
+        <v>43800</v>
       </c>
       <c r="H60" s="3">
-        <v>48000</v>
+        <v>45400</v>
       </c>
       <c r="I60" s="3">
-        <v>50300</v>
+        <v>49000</v>
       </c>
       <c r="J60" s="3">
+        <v>51400</v>
+      </c>
+      <c r="K60" s="3">
         <v>50500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>57100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>55300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>57000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>64100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>85800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>81300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>79800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>83500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>85800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>78700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>97200</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4221,8 +4361,11 @@
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4295,68 +4438,71 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>300</v>
+      </c>
+      <c r="E62" s="3">
         <v>200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
+        <v>3800</v>
+      </c>
+      <c r="J62" s="3">
+        <v>2600</v>
+      </c>
+      <c r="K62" s="3">
+        <v>2700</v>
+      </c>
+      <c r="L62" s="3">
+        <v>2800</v>
+      </c>
+      <c r="M62" s="3">
+        <v>4100</v>
+      </c>
+      <c r="N62" s="3">
+        <v>3300</v>
+      </c>
+      <c r="O62" s="3">
         <v>3700</v>
       </c>
-      <c r="I62" s="3">
-        <v>2500</v>
-      </c>
-      <c r="J62" s="3">
-        <v>2700</v>
-      </c>
-      <c r="K62" s="3">
-        <v>2800</v>
-      </c>
-      <c r="L62" s="3">
-        <v>4100</v>
-      </c>
-      <c r="M62" s="3">
-        <v>3300</v>
-      </c>
-      <c r="N62" s="3">
-        <v>3700</v>
-      </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>4200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>4300</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>1100</v>
       </c>
       <c r="R62" s="3">
         <v>1100</v>
       </c>
       <c r="S62" s="3">
+        <v>1100</v>
+      </c>
+      <c r="T62" s="3">
         <v>1200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2800</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4369,8 +4515,11 @@
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4443,8 +4592,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4517,8 +4669,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4591,68 +4746,71 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>44000</v>
+        <v>49300</v>
       </c>
       <c r="E66" s="3">
-        <v>48200</v>
+        <v>44900</v>
       </c>
       <c r="F66" s="3">
-        <v>50600</v>
+        <v>49200</v>
       </c>
       <c r="G66" s="3">
-        <v>52100</v>
+        <v>51600</v>
       </c>
       <c r="H66" s="3">
-        <v>57600</v>
+        <v>53200</v>
       </c>
       <c r="I66" s="3">
-        <v>52900</v>
+        <v>58800</v>
       </c>
       <c r="J66" s="3">
+        <v>53900</v>
+      </c>
+      <c r="K66" s="3">
         <v>53200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>59900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>59400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>60300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>67800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>89900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>85700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>80900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>84600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>87000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>80800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>100000</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4665,8 +4823,11 @@
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4693,8 +4854,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4767,8 +4929,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4841,8 +5006,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4895,14 +5063,14 @@
         <v>0</v>
       </c>
       <c r="T70" s="3">
+        <v>0</v>
+      </c>
+      <c r="U70" s="3">
         <v>1261300</v>
       </c>
-      <c r="U70" s="3">
+      <c r="V70" s="3">
         <v>1040100</v>
       </c>
-      <c r="V70" s="3">
-        <v>0</v>
-      </c>
       <c r="W70" s="3">
         <v>0</v>
       </c>
@@ -4915,8 +5083,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4989,68 +5160,71 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-1219900</v>
+        <v>-1248100</v>
       </c>
       <c r="E72" s="3">
-        <v>-1214800</v>
+        <v>-1244800</v>
       </c>
       <c r="F72" s="3">
-        <v>-1198100</v>
+        <v>-1239600</v>
       </c>
       <c r="G72" s="3">
-        <v>-1190200</v>
+        <v>-1222600</v>
       </c>
       <c r="H72" s="3">
-        <v>-1158700</v>
+        <v>-1214500</v>
       </c>
       <c r="I72" s="3">
-        <v>-1115000</v>
+        <v>-1182300</v>
       </c>
       <c r="J72" s="3">
+        <v>-1137700</v>
+      </c>
+      <c r="K72" s="3">
         <v>-1101800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1086100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1112900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1076800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1126800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1174900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-903900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-864900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-825000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-767100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-743400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-668400</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5063,8 +5237,11 @@
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5137,8 +5314,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5211,8 +5391,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5285,68 +5468,71 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>84200</v>
+        <v>83000</v>
       </c>
       <c r="E76" s="3">
-        <v>88100</v>
+        <v>86000</v>
       </c>
       <c r="F76" s="3">
-        <v>104600</v>
+        <v>89900</v>
       </c>
       <c r="G76" s="3">
-        <v>109100</v>
+        <v>106700</v>
       </c>
       <c r="H76" s="3">
-        <v>141200</v>
+        <v>111300</v>
       </c>
       <c r="I76" s="3">
-        <v>186000</v>
+        <v>144000</v>
       </c>
       <c r="J76" s="3">
+        <v>189800</v>
+      </c>
+      <c r="K76" s="3">
         <v>201000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>214800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>236900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>263100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>291800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>329300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>575000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>623300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>615700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>604600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-711600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-642200</v>
       </c>
-      <c r="V76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5359,8 +5545,11 @@
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5433,161 +5622,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44834</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44651</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44469</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44377</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44286</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44196</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44104</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44012</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>43921</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>43830</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>43738</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43646</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43555</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43465</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43373</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43281</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43190</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43100</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43008</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>42916</v>
       </c>
-      <c r="Z80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-4900</v>
+        <v>-3400</v>
       </c>
       <c r="E81" s="3">
-        <v>-16700</v>
+        <v>-5000</v>
       </c>
       <c r="F81" s="3">
-        <v>-7900</v>
+        <v>-17000</v>
       </c>
       <c r="G81" s="3">
-        <v>-31200</v>
+        <v>-8100</v>
       </c>
       <c r="H81" s="3">
-        <v>-44000</v>
+        <v>-31800</v>
       </c>
       <c r="I81" s="3">
-        <v>-13200</v>
+        <v>-44900</v>
       </c>
       <c r="J81" s="3">
+        <v>-13500</v>
+      </c>
+      <c r="K81" s="3">
         <v>-15000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-5100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-13300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-12400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-20900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-255900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-50300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-18800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-21400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-26300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-65900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-43300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>3700</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X81" s="3">
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y81" s="3">
         <v>-63300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-49600</v>
       </c>
-      <c r="Z81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5614,8 +5812,9 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5664,32 +5863,35 @@
       <c r="R83" s="3">
         <v>0</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T83" s="3">
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+      <c r="T83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U83" s="3">
         <v>8500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>4500</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X83" s="3">
+      <c r="X83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y83" s="3">
         <v>18700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>18900</v>
       </c>
-      <c r="Z83" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5762,8 +5964,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5836,8 +6041,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5910,8 +6118,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5984,8 +6195,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6058,82 +6272,88 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="F89" s="3">
+        <v>800</v>
+      </c>
+      <c r="G89" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="H89" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="I89" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="J89" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="K89" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="L89" s="3">
+        <v>1700</v>
+      </c>
+      <c r="M89" s="3">
         <v>-4500</v>
       </c>
-      <c r="E89" s="3">
-        <v>800</v>
-      </c>
-      <c r="F89" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="G89" s="3">
-        <v>-5600</v>
-      </c>
-      <c r="H89" s="3">
-        <v>-8600</v>
-      </c>
-      <c r="I89" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="J89" s="3">
-        <v>-6900</v>
-      </c>
-      <c r="K89" s="3">
-        <v>1700</v>
-      </c>
-      <c r="L89" s="3">
-        <v>-4500</v>
-      </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-22800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-5900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-13800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-4700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-13800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>4200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-35800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-2500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-19700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-18600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>26100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-33900</v>
       </c>
-      <c r="Z89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6160,8 +6380,9 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6210,32 +6431,35 @@
       <c r="R91" s="3">
         <v>0</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T91" s="3">
-        <v>-200</v>
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U91" s="3">
         <v>-200</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>3</v>
+      <c r="V91" s="3">
+        <v>-200</v>
       </c>
       <c r="W91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X91" s="3">
-        <v>-300</v>
+      <c r="X91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y91" s="3">
         <v>-300</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AA91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6308,8 +6532,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6382,82 +6609,88 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2900</v>
       </c>
-      <c r="E94" s="3">
-        <v>4000</v>
-      </c>
       <c r="F94" s="3">
-        <v>-3900</v>
+        <v>4100</v>
       </c>
       <c r="G94" s="3">
-        <v>-4900</v>
+        <v>-4000</v>
       </c>
       <c r="H94" s="3">
-        <v>-4500</v>
+        <v>-5000</v>
       </c>
       <c r="I94" s="3">
-        <v>11300</v>
+        <v>-4600</v>
       </c>
       <c r="J94" s="3">
+        <v>11600</v>
+      </c>
+      <c r="K94" s="3">
         <v>-8300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>13000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-16600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>20900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>2000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-22900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-18600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>21400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-11400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-12800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-7900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>11800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>33600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>11500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-6800</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6484,8 +6717,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6558,8 +6792,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6632,8 +6869,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6706,8 +6946,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6780,8 +7023,11 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -6789,217 +7035,226 @@
         <v>0</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>-1300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="K100" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="L100" s="3">
         <v>-1000</v>
       </c>
-      <c r="J100" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="K100" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-13800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-3500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>61800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1600</v>
-      </c>
-      <c r="U100" s="3">
-        <v>100</v>
       </c>
       <c r="V100" s="3">
         <v>100</v>
       </c>
       <c r="W100" s="3">
+        <v>100</v>
+      </c>
+      <c r="X100" s="3">
         <v>300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>200</v>
       </c>
-      <c r="Z100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E101" s="3">
         <v>500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-100</v>
       </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
       <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
         <v>-400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1600</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
       <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3">
         <v>800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>2700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>2600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-2500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-200</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>3900</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>5200</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-4400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-2000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z101" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-7000</v>
+        <v>-1000</v>
       </c>
       <c r="E102" s="3">
-        <v>3200</v>
+        <v>-7100</v>
       </c>
       <c r="F102" s="3">
-        <v>-6300</v>
+        <v>3300</v>
       </c>
       <c r="G102" s="3">
-        <v>-9500</v>
+        <v>-6400</v>
       </c>
       <c r="H102" s="3">
-        <v>-13200</v>
+        <v>-9600</v>
       </c>
       <c r="I102" s="3">
-        <v>8300</v>
+        <v>-13400</v>
       </c>
       <c r="J102" s="3">
+        <v>8500</v>
+      </c>
+      <c r="K102" s="3">
         <v>-16200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>12100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-36400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-4000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-5100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-36900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-21700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>54400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-43200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-5000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-12100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>13400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>35100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-42800</v>
       </c>
-      <c r="Z102" s="3" t="s">
+      <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MOGU_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MOGU_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="92">
   <si>
     <t>MOGU</t>
   </si>
@@ -656,354 +656,379 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="I7" s="2">
+        <v>45107</v>
+      </c>
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
-        <v>44834</v>
-      </c>
-      <c r="H7" s="2">
-        <v>44651</v>
-      </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44469</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44377</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44286</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44196</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44104</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44012</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>43921</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>43830</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43738</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43646</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43555</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43465</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43373</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43281</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43190</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43100</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43008</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>42916</v>
       </c>
-      <c r="AA7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AC7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E8" s="3">
+        <v>4300</v>
+      </c>
+      <c r="F8" s="3">
+        <v>5300</v>
+      </c>
+      <c r="G8" s="3">
+        <v>5400</v>
+      </c>
+      <c r="H8" s="3">
+        <v>5700</v>
+      </c>
+      <c r="I8" s="3">
+        <v>5700</v>
+      </c>
+      <c r="J8" s="3">
+        <v>8500</v>
+      </c>
+      <c r="K8" s="3">
         <v>10900</v>
       </c>
-      <c r="E8" s="3">
-        <v>11700</v>
-      </c>
-      <c r="F8" s="3">
-        <v>16500</v>
-      </c>
-      <c r="G8" s="3">
-        <v>16200</v>
-      </c>
-      <c r="H8" s="3">
-        <v>23700</v>
-      </c>
-      <c r="I8" s="3">
-        <v>10900</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>13000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>12600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>20200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>16000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>18400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>17500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>42200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>30500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>38800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>33100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>53300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>33900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>35800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>26900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>45300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>32000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>39300</v>
       </c>
-      <c r="AA8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AC8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E9" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F9" s="3">
+        <v>2900</v>
+      </c>
+      <c r="G9" s="3">
+        <v>2900</v>
+      </c>
+      <c r="H9" s="3">
+        <v>3400</v>
+      </c>
+      <c r="I9" s="3">
+        <v>3400</v>
+      </c>
+      <c r="J9" s="3">
+        <v>3900</v>
+      </c>
+      <c r="K9" s="3">
         <v>5900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="L9" s="3">
+        <v>6100</v>
+      </c>
+      <c r="M9" s="3">
+        <v>5200</v>
+      </c>
+      <c r="N9" s="3">
         <v>7000</v>
       </c>
-      <c r="F9" s="3">
-        <v>7600</v>
-      </c>
-      <c r="G9" s="3">
-        <v>8400</v>
-      </c>
-      <c r="H9" s="3">
-        <v>10500</v>
-      </c>
-      <c r="I9" s="3">
-        <v>5900</v>
-      </c>
-      <c r="J9" s="3">
-        <v>6100</v>
-      </c>
-      <c r="K9" s="3">
-        <v>5200</v>
-      </c>
-      <c r="L9" s="3">
-        <v>7000</v>
-      </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>6500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>6800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>8600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>15400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>11700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>9500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>9300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>14600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>11500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>10300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>10900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>12300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>11600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>12000</v>
       </c>
-      <c r="AA9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AC9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>5000</v>
+        <v>1600</v>
       </c>
       <c r="E10" s="3">
-        <v>4800</v>
+        <v>1500</v>
       </c>
       <c r="F10" s="3">
+        <v>2500</v>
+      </c>
+      <c r="G10" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H10" s="3">
+        <v>2300</v>
+      </c>
+      <c r="I10" s="3">
+        <v>2300</v>
+      </c>
+      <c r="J10" s="3">
+        <v>4600</v>
+      </c>
+      <c r="K10" s="3">
+        <v>5100</v>
+      </c>
+      <c r="L10" s="3">
+        <v>6800</v>
+      </c>
+      <c r="M10" s="3">
+        <v>7300</v>
+      </c>
+      <c r="N10" s="3">
+        <v>13200</v>
+      </c>
+      <c r="O10" s="3">
+        <v>9500</v>
+      </c>
+      <c r="P10" s="3">
+        <v>11700</v>
+      </c>
+      <c r="Q10" s="3">
         <v>8900</v>
       </c>
-      <c r="G10" s="3">
-        <v>7800</v>
-      </c>
-      <c r="H10" s="3">
-        <v>13200</v>
-      </c>
-      <c r="I10" s="3">
-        <v>5100</v>
-      </c>
-      <c r="J10" s="3">
-        <v>6800</v>
-      </c>
-      <c r="K10" s="3">
-        <v>7300</v>
-      </c>
-      <c r="L10" s="3">
-        <v>13200</v>
-      </c>
-      <c r="M10" s="3">
-        <v>9500</v>
-      </c>
-      <c r="N10" s="3">
-        <v>11700</v>
-      </c>
-      <c r="O10" s="3">
-        <v>8900</v>
-      </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>26800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>18800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>29400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>23800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>38700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>22500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>25600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>16000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>33000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>20400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>27300</v>
       </c>
-      <c r="AA10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AC10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1031,85 +1056,93 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>1800</v>
+        <v>900</v>
       </c>
       <c r="E12" s="3">
-        <v>2000</v>
+        <v>800</v>
       </c>
       <c r="F12" s="3">
-        <v>2300</v>
+        <v>900</v>
       </c>
       <c r="G12" s="3">
-        <v>2900</v>
+        <v>900</v>
       </c>
       <c r="H12" s="3">
-        <v>5300</v>
+        <v>1000</v>
       </c>
       <c r="I12" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J12" s="3">
+        <v>1200</v>
+      </c>
+      <c r="K12" s="3">
         <v>3300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>3100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>2700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>3800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>3900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>4000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>4800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>5000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>7700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>8800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>8700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>8000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>8800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>8800</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>10000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>10500</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>11300</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>10800</v>
       </c>
-      <c r="AA12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1185,35 +1218,41 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>1400</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F14" s="3">
-        <v>11900</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
       </c>
       <c r="H14" s="3">
-        <v>6900</v>
+        <v>700</v>
       </c>
       <c r="I14" s="3">
+        <v>700</v>
+      </c>
+      <c r="J14" s="3">
+        <v>6100</v>
+      </c>
+      <c r="K14" s="3">
         <v>26300</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1223,47 +1262,53 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>216400</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>3</v>
+      <c r="V14" s="3">
+        <v>0</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
       </c>
-      <c r="X14" s="3">
+      <c r="X14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA14" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1271,76 +1316,82 @@
         <v>0</v>
       </c>
       <c r="E15" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="F15" s="3">
-        <v>5600</v>
+        <v>0</v>
       </c>
       <c r="G15" s="3">
-        <v>2800</v>
+        <v>0</v>
       </c>
       <c r="H15" s="3">
-        <v>23700</v>
+        <v>100</v>
       </c>
       <c r="I15" s="3">
+        <v>100</v>
+      </c>
+      <c r="J15" s="3">
+        <v>2900</v>
+      </c>
+      <c r="K15" s="3">
         <v>13500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>9100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>11300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>15700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>10800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>9800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>12800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>16100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>11800</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>10100</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>6800</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>9700</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>8000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>3900</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Y15" s="3">
         <v>7900</v>
-      </c>
-      <c r="X15" s="3">
-        <v>16300</v>
-      </c>
-      <c r="Y15" s="3">
-        <v>16300</v>
       </c>
       <c r="Z15" s="3">
         <v>16300</v>
       </c>
-      <c r="AA15" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>16300</v>
+      </c>
+      <c r="AB15" s="3">
+        <v>16300</v>
+      </c>
+      <c r="AC15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1365,162 +1416,176 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>14700</v>
+        <v>7400</v>
       </c>
       <c r="E17" s="3">
-        <v>19100</v>
+        <v>7100</v>
       </c>
       <c r="F17" s="3">
-        <v>36200</v>
+        <v>7200</v>
       </c>
       <c r="G17" s="3">
-        <v>23000</v>
+        <v>7400</v>
       </c>
       <c r="H17" s="3">
-        <v>57600</v>
+        <v>8600</v>
       </c>
       <c r="I17" s="3">
+        <v>8600</v>
+      </c>
+      <c r="J17" s="3">
+        <v>11900</v>
+      </c>
+      <c r="K17" s="3">
         <v>57800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>26800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>27800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>37300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>30300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>31700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>39500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>291900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>64900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>55300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>58700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>67500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>61800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>52100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>47900</v>
       </c>
-      <c r="X17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA17" s="3">
         <v>76000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>69400</v>
       </c>
-      <c r="AA17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AC17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-3800</v>
+        <v>-3000</v>
       </c>
       <c r="E18" s="3">
-        <v>-7300</v>
+        <v>-2900</v>
       </c>
       <c r="F18" s="3">
-        <v>-19700</v>
+        <v>-1900</v>
       </c>
       <c r="G18" s="3">
-        <v>-6800</v>
+        <v>-1900</v>
       </c>
       <c r="H18" s="3">
-        <v>-33900</v>
+        <v>-2900</v>
       </c>
       <c r="I18" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="K18" s="3">
         <v>-46800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-13800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-15200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-17000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-14300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-13200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-22000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-249700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-34400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-16400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-25600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-14200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-27900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-16300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-20900</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA18" s="3">
         <v>-44000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-30100</v>
       </c>
-      <c r="AA18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AC18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1548,170 +1613,184 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
+        <v>200</v>
+      </c>
+      <c r="G20" s="3">
+        <v>200</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
+        <v>500</v>
+      </c>
+      <c r="K20" s="3">
+        <v>1800</v>
+      </c>
+      <c r="L20" s="3">
+        <v>300</v>
+      </c>
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
+        <v>13300</v>
+      </c>
+      <c r="O20" s="3">
+        <v>800</v>
+      </c>
+      <c r="P20" s="3">
         <v>700</v>
       </c>
-      <c r="E20" s="3">
-        <v>1200</v>
-      </c>
-      <c r="F20" s="3">
+      <c r="Q20" s="3">
+        <v>900</v>
+      </c>
+      <c r="R20" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="S20" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="T20" s="3">
         <v>1300</v>
       </c>
-      <c r="G20" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I20" s="3">
-        <v>1800</v>
-      </c>
-      <c r="J20" s="3">
-        <v>300</v>
-      </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3">
-        <v>13300</v>
-      </c>
-      <c r="M20" s="3">
-        <v>800</v>
-      </c>
-      <c r="N20" s="3">
-        <v>700</v>
-      </c>
-      <c r="O20" s="3">
+      <c r="U20" s="3">
+        <v>1400</v>
+      </c>
+      <c r="V20" s="3">
+        <v>5700</v>
+      </c>
+      <c r="W20" s="3">
+        <v>1300</v>
+      </c>
+      <c r="X20" s="3">
+        <v>1100</v>
+      </c>
+      <c r="Y20" s="3">
+        <v>23700</v>
+      </c>
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA20" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AB20" s="3">
         <v>900</v>
       </c>
-      <c r="P20" s="3">
-        <v>-4100</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>-3900</v>
-      </c>
-      <c r="R20" s="3">
-        <v>1300</v>
-      </c>
-      <c r="S20" s="3">
-        <v>1400</v>
-      </c>
-      <c r="T20" s="3">
-        <v>5700</v>
-      </c>
-      <c r="U20" s="3">
-        <v>1300</v>
-      </c>
-      <c r="V20" s="3">
-        <v>1100</v>
-      </c>
-      <c r="W20" s="3">
-        <v>23700</v>
-      </c>
-      <c r="X20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>1900</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>900</v>
-      </c>
-      <c r="AA20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="K21" s="3">
+        <v>-40700</v>
+      </c>
+      <c r="L21" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="M21" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="N21" s="3">
+        <v>1800</v>
+      </c>
+      <c r="O21" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="P21" s="3">
         <v>-2500</v>
       </c>
-      <c r="E21" s="3">
-        <v>-5400</v>
-      </c>
-      <c r="F21" s="3">
-        <v>-15400</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-5200</v>
-      </c>
-      <c r="H21" s="3">
-        <v>-23600</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-40700</v>
-      </c>
-      <c r="J21" s="3">
-        <v>-4200</v>
-      </c>
-      <c r="K21" s="3">
-        <v>-20000</v>
-      </c>
-      <c r="L21" s="3">
-        <v>1800</v>
-      </c>
-      <c r="M21" s="3">
-        <v>-12700</v>
-      </c>
-      <c r="N21" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-23400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-249700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-36400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-4800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-3300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-11600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-18100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-10700</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y21" s="3">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA21" s="3">
         <v>-23300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>-10300</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F22" s="3">
         <v>0</v>
@@ -1719,11 +1798,11 @@
       <c r="G22" s="3">
         <v>0</v>
       </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J22" s="3">
         <v>0</v>
@@ -1779,85 +1858,97 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-3100</v>
+        <v>-1600</v>
       </c>
       <c r="E23" s="3">
-        <v>-6200</v>
+        <v>-1600</v>
       </c>
       <c r="F23" s="3">
-        <v>-18400</v>
+        <v>-1700</v>
       </c>
       <c r="G23" s="3">
-        <v>-8300</v>
+        <v>-1700</v>
       </c>
       <c r="H23" s="3">
-        <v>-34000</v>
+        <v>-3000</v>
       </c>
       <c r="I23" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="J23" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="K23" s="3">
         <v>-45100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-13500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-15300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-3800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-13500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-12500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-21100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-253800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-38300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-15100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-24200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-8500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-26600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-15200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>2700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-26800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-42100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-29200</v>
       </c>
-      <c r="AA23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AC23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1865,76 +1956,82 @@
         <v>0</v>
       </c>
       <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K24" s="3">
         <v>-200</v>
       </c>
-      <c r="F24" s="3">
-        <v>-100</v>
-      </c>
-      <c r="G24" s="3">
-        <v>-200</v>
-      </c>
-      <c r="H24" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="I24" s="3">
-        <v>-200</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>-300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>1300</v>
-      </c>
-      <c r="M24" s="3">
-        <v>-200</v>
-      </c>
-      <c r="N24" s="3">
-        <v>-200</v>
       </c>
       <c r="O24" s="3">
         <v>-200</v>
       </c>
       <c r="P24" s="3">
-        <v>100</v>
+        <v>-200</v>
       </c>
       <c r="Q24" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="R24" s="3">
         <v>100</v>
       </c>
       <c r="S24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="T24" s="3">
+        <v>100</v>
+      </c>
+      <c r="U24" s="3">
         <v>-700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>-300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>-800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>-700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>-1700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>-3700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>-3800</v>
       </c>
-      <c r="AA24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AC24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2010,162 +2107,180 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-3100</v>
+        <v>-1600</v>
       </c>
       <c r="E26" s="3">
-        <v>-5900</v>
+        <v>-1600</v>
       </c>
       <c r="F26" s="3">
-        <v>-18300</v>
+        <v>-1700</v>
       </c>
       <c r="G26" s="3">
-        <v>-8100</v>
+        <v>-1700</v>
       </c>
       <c r="H26" s="3">
-        <v>-32200</v>
+        <v>-2900</v>
       </c>
       <c r="I26" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="J26" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="K26" s="3">
         <v>-44800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-13500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-15000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-5100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-13300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-12400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-20900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-254000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-38200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-15200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-23400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-8300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-25800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-14500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>4400</v>
       </c>
-      <c r="X26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA26" s="3">
         <v>-38200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-25300</v>
       </c>
-      <c r="AA26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AC26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-3400</v>
+        <v>-1700</v>
       </c>
       <c r="E27" s="3">
-        <v>-5000</v>
+        <v>-1700</v>
       </c>
       <c r="F27" s="3">
-        <v>-17000</v>
+        <v>-1700</v>
       </c>
       <c r="G27" s="3">
-        <v>-8100</v>
+        <v>-1700</v>
       </c>
       <c r="H27" s="3">
-        <v>-31800</v>
+        <v>-2400</v>
       </c>
       <c r="I27" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="J27" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="K27" s="3">
         <v>-44900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-13500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-15000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-5100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-13300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-12400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-20900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-255900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-50300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-18800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-21400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-26300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-65900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-43300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>3700</v>
       </c>
-      <c r="X27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA27" s="3">
         <v>-63300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-49600</v>
       </c>
-      <c r="AA27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AC27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2241,8 +2356,14 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2318,8 +2439,14 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2395,8 +2522,14 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2472,162 +2605,180 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="G32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="K32" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="L32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
+        <v>-13300</v>
+      </c>
+      <c r="O32" s="3">
+        <v>-800</v>
+      </c>
+      <c r="P32" s="3">
         <v>-700</v>
       </c>
-      <c r="E32" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="F32" s="3">
+      <c r="Q32" s="3">
+        <v>-900</v>
+      </c>
+      <c r="R32" s="3">
+        <v>4100</v>
+      </c>
+      <c r="S32" s="3">
+        <v>3900</v>
+      </c>
+      <c r="T32" s="3">
         <v>-1300</v>
       </c>
-      <c r="G32" s="3">
-        <v>1500</v>
-      </c>
-      <c r="H32" s="3">
-        <v>100</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-300</v>
-      </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-13300</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-800</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-700</v>
-      </c>
-      <c r="O32" s="3">
+      <c r="U32" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="V32" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="W32" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="X32" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="Y32" s="3">
+        <v>-23700</v>
+      </c>
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA32" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="AB32" s="3">
         <v>-900</v>
       </c>
-      <c r="P32" s="3">
-        <v>4100</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>3900</v>
-      </c>
-      <c r="R32" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="S32" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="T32" s="3">
-        <v>-5700</v>
-      </c>
-      <c r="U32" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="V32" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="W32" s="3">
-        <v>-23700</v>
-      </c>
-      <c r="X32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>-900</v>
-      </c>
-      <c r="AA32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-3400</v>
+        <v>-1700</v>
       </c>
       <c r="E33" s="3">
-        <v>-5000</v>
+        <v>-1700</v>
       </c>
       <c r="F33" s="3">
-        <v>-17000</v>
+        <v>-1700</v>
       </c>
       <c r="G33" s="3">
-        <v>-8100</v>
+        <v>-1700</v>
       </c>
       <c r="H33" s="3">
-        <v>-31800</v>
+        <v>-2400</v>
       </c>
       <c r="I33" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="J33" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="K33" s="3">
         <v>-44900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-13500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-15000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-5100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-13300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-12400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-20900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-255900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-50300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-18800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-21400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-26300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-65900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-43300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>3700</v>
       </c>
-      <c r="X33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA33" s="3">
         <v>-63300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-49600</v>
       </c>
-      <c r="AA33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AC33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2703,167 +2854,185 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-3400</v>
+        <v>-1700</v>
       </c>
       <c r="E35" s="3">
-        <v>-5000</v>
+        <v>-1700</v>
       </c>
       <c r="F35" s="3">
-        <v>-17000</v>
+        <v>-1700</v>
       </c>
       <c r="G35" s="3">
-        <v>-8100</v>
+        <v>-1700</v>
       </c>
       <c r="H35" s="3">
-        <v>-31800</v>
+        <v>-2400</v>
       </c>
       <c r="I35" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="J35" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="K35" s="3">
         <v>-44900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-13500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-15000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-5100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-13300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-12400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-20900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-255900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-50300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-18800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-21400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-26300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-65900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-43300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>3700</v>
       </c>
-      <c r="X35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA35" s="3">
         <v>-63300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-49600</v>
       </c>
-      <c r="AA35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AC35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="I38" s="2">
+        <v>45107</v>
+      </c>
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
-        <v>44834</v>
-      </c>
-      <c r="H38" s="2">
-        <v>44651</v>
-      </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44469</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44377</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44286</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44196</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44104</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44012</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>43921</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>43830</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43738</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43646</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43555</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43465</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43373</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43281</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43190</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43100</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43008</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>42916</v>
       </c>
-      <c r="AA38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AC38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2891,8 +3060,10 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2920,74 +3091,76 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>11600</v>
+      </c>
+      <c r="F41" s="3">
+        <v>49700</v>
+      </c>
+      <c r="G41" s="3">
         <v>50600</v>
       </c>
-      <c r="E41" s="3">
-        <v>51600</v>
-      </c>
-      <c r="F41" s="3">
-        <v>58700</v>
-      </c>
-      <c r="G41" s="3">
-        <v>55400</v>
-      </c>
       <c r="H41" s="3">
-        <v>61800</v>
+        <v>50200</v>
       </c>
       <c r="I41" s="3">
+        <v>50500</v>
+      </c>
+      <c r="J41" s="3">
+        <v>60600</v>
+      </c>
+      <c r="K41" s="3">
         <v>71500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>84900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>74900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>91000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>81300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>115200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>126200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>135500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>138300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>177500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>194200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>183900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>129500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>166400</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2997,74 +3170,80 @@
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>38700</v>
+      </c>
+      <c r="E42" s="3">
+        <v>37400</v>
+      </c>
+      <c r="F42" s="3">
         <v>8600</v>
       </c>
-      <c r="E42" s="3">
-        <v>14600</v>
-      </c>
-      <c r="F42" s="3">
-        <v>20600</v>
-      </c>
       <c r="G42" s="3">
-        <v>29800</v>
+        <v>8700</v>
       </c>
       <c r="H42" s="3">
-        <v>27800</v>
+        <v>14200</v>
       </c>
       <c r="I42" s="3">
+        <v>14300</v>
+      </c>
+      <c r="J42" s="3">
+        <v>21600</v>
+      </c>
+      <c r="K42" s="3">
         <v>15300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>24400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>36000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>22100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>32700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>30600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>35100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>50900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>59900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>50500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>32200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>50400</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>44400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>32200</v>
       </c>
-      <c r="W42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3074,74 +3253,80 @@
       <c r="AA42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>8300</v>
+        <v>4100</v>
       </c>
       <c r="E43" s="3">
+        <v>4000</v>
+      </c>
+      <c r="F43" s="3">
+        <v>7900</v>
+      </c>
+      <c r="G43" s="3">
+        <v>8000</v>
+      </c>
+      <c r="H43" s="3">
         <v>600</v>
       </c>
-      <c r="F43" s="3">
-        <v>1200</v>
-      </c>
-      <c r="G43" s="3">
-        <v>1500</v>
-      </c>
-      <c r="H43" s="3">
-        <v>5100</v>
-      </c>
       <c r="I43" s="3">
+        <v>600</v>
+      </c>
+      <c r="J43" s="3">
+        <v>10600</v>
+      </c>
+      <c r="K43" s="3">
         <v>11700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>13900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>17600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>19400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>16100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>16500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>16700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>27900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>21600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>18900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>18700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>19200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>27400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>30000</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3151,8 +3336,14 @@
       <c r="AA43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3181,44 +3372,44 @@
         <v>0</v>
       </c>
       <c r="L44" s="3">
+        <v>0</v>
+      </c>
+      <c r="M44" s="3">
+        <v>0</v>
+      </c>
+      <c r="N44" s="3">
         <v>100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>2200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>100</v>
       </c>
-      <c r="W44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3228,74 +3419,80 @@
       <c r="AA44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>4100</v>
+        <v>13600</v>
       </c>
       <c r="E45" s="3">
-        <v>14000</v>
+        <v>13200</v>
       </c>
       <c r="F45" s="3">
-        <v>9900</v>
+        <v>500</v>
       </c>
       <c r="G45" s="3">
-        <v>7700</v>
+        <v>500</v>
       </c>
       <c r="H45" s="3">
-        <v>6600</v>
+        <v>13600</v>
       </c>
       <c r="I45" s="3">
+        <v>13700</v>
+      </c>
+      <c r="J45" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K45" s="3">
         <v>8700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>9300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>7900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>13800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>11800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>11800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>14700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>18600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>22100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>24400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>24700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>23900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>7300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>6300</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3305,74 +3502,80 @@
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>68600</v>
+      </c>
+      <c r="E46" s="3">
+        <v>66200</v>
+      </c>
+      <c r="F46" s="3">
+        <v>70300</v>
+      </c>
+      <c r="G46" s="3">
         <v>71600</v>
       </c>
-      <c r="E46" s="3">
-        <v>80900</v>
-      </c>
-      <c r="F46" s="3">
-        <v>90300</v>
-      </c>
-      <c r="G46" s="3">
-        <v>94400</v>
-      </c>
       <c r="H46" s="3">
-        <v>101400</v>
+        <v>78700</v>
       </c>
       <c r="I46" s="3">
+        <v>79200</v>
+      </c>
+      <c r="J46" s="3">
+        <v>96900</v>
+      </c>
+      <c r="K46" s="3">
         <v>107200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>132500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>136400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>146400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>142100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>174500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>193100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>235000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>242400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>272100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>270600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>278000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>208700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>234900</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3382,74 +3585,80 @@
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E47" s="3">
+        <v>7400</v>
+      </c>
+      <c r="F47" s="3">
+        <v>11300</v>
+      </c>
+      <c r="G47" s="3">
         <v>11500</v>
       </c>
-      <c r="E47" s="3">
-        <v>11600</v>
-      </c>
-      <c r="F47" s="3">
-        <v>9800</v>
-      </c>
-      <c r="G47" s="3">
-        <v>8700</v>
-      </c>
       <c r="H47" s="3">
-        <v>10200</v>
+        <v>11300</v>
       </c>
       <c r="I47" s="3">
+        <v>11300</v>
+      </c>
+      <c r="J47" s="3">
+        <v>10100</v>
+      </c>
+      <c r="K47" s="3">
         <v>11200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>10300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>9200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>8600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>17200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>15900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>15100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>11300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>17300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>34200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>36800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>32000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>29200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>27600</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3459,74 +3668,80 @@
       <c r="AA47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>43000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>41500</v>
+      </c>
+      <c r="F48" s="3">
+        <v>41900</v>
+      </c>
+      <c r="G48" s="3">
         <v>42600</v>
       </c>
-      <c r="E48" s="3">
-        <v>31600</v>
-      </c>
-      <c r="F48" s="3">
-        <v>28200</v>
-      </c>
-      <c r="G48" s="3">
-        <v>2600</v>
-      </c>
       <c r="H48" s="3">
-        <v>1100</v>
+        <v>30800</v>
       </c>
       <c r="I48" s="3">
+        <v>30900</v>
+      </c>
+      <c r="J48" s="3">
+        <v>29100</v>
+      </c>
+      <c r="K48" s="3">
         <v>1400</v>
-      </c>
-      <c r="J48" s="3">
-        <v>1500</v>
-      </c>
-      <c r="K48" s="3">
-        <v>1500</v>
       </c>
       <c r="L48" s="3">
         <v>1500</v>
       </c>
       <c r="M48" s="3">
+        <v>1500</v>
+      </c>
+      <c r="N48" s="3">
+        <v>1500</v>
+      </c>
+      <c r="O48" s="3">
         <v>2000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>1800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>2100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>2300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>2400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>2100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>1800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>1600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>1500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>1700</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3536,8 +3751,14 @@
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3548,62 +3769,62 @@
         <v>100</v>
       </c>
       <c r="F49" s="3">
+        <v>100</v>
+      </c>
+      <c r="G49" s="3">
+        <v>100</v>
+      </c>
+      <c r="H49" s="3">
+        <v>100</v>
+      </c>
+      <c r="I49" s="3">
+        <v>100</v>
+      </c>
+      <c r="J49" s="3">
         <v>1800</v>
       </c>
-      <c r="G49" s="3">
-        <v>19400</v>
-      </c>
-      <c r="H49" s="3">
-        <v>21600</v>
-      </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>52700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>76400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>84600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>95600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>117800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>129200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>147300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>168300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>396000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>395600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>391000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>378700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>388200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>232000</v>
       </c>
-      <c r="W49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3613,8 +3834,14 @@
       <c r="AA49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3690,8 +3917,14 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3767,74 +4000,80 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>6800</v>
+      </c>
+      <c r="F52" s="3">
+        <v>6300</v>
+      </c>
+      <c r="G52" s="3">
         <v>6400</v>
       </c>
-      <c r="E52" s="3">
-        <v>6500</v>
-      </c>
-      <c r="F52" s="3">
-        <v>9000</v>
-      </c>
-      <c r="G52" s="3">
-        <v>33300</v>
-      </c>
       <c r="H52" s="3">
-        <v>30300</v>
+        <v>6400</v>
       </c>
       <c r="I52" s="3">
+        <v>6400</v>
+      </c>
+      <c r="J52" s="3">
+        <v>9300</v>
+      </c>
+      <c r="K52" s="3">
         <v>30400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>23100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>22500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>22500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>17200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>2000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>2100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>2200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>2700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>1300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>2900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>1600</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3844,8 +4083,14 @@
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3921,74 +4166,80 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>126500</v>
+      </c>
+      <c r="E54" s="3">
+        <v>122100</v>
+      </c>
+      <c r="F54" s="3">
+        <v>130000</v>
+      </c>
+      <c r="G54" s="3">
         <v>132300</v>
       </c>
-      <c r="E54" s="3">
-        <v>130900</v>
-      </c>
-      <c r="F54" s="3">
-        <v>139000</v>
-      </c>
-      <c r="G54" s="3">
-        <v>158400</v>
-      </c>
       <c r="H54" s="3">
-        <v>164500</v>
+        <v>127200</v>
       </c>
       <c r="I54" s="3">
+        <v>128000</v>
+      </c>
+      <c r="J54" s="3">
+        <v>147200</v>
+      </c>
+      <c r="K54" s="3">
         <v>202800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>243700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>254200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>274700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>296300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>323400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>359700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>419200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>660700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>704100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>700300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>691600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>630600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>497800</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3998,8 +4249,14 @@
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4027,8 +4284,10 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4056,74 +4315,76 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>500</v>
+      </c>
+      <c r="E57" s="3">
+        <v>500</v>
+      </c>
+      <c r="F57" s="3">
         <v>1000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H57" s="3">
         <v>900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="I57" s="3">
+        <v>900</v>
+      </c>
+      <c r="J57" s="3">
         <v>1200</v>
       </c>
-      <c r="G57" s="3">
-        <v>2200</v>
-      </c>
-      <c r="H57" s="3">
+      <c r="K57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="L57" s="3">
+        <v>2600</v>
+      </c>
+      <c r="M57" s="3">
+        <v>2800</v>
+      </c>
+      <c r="N57" s="3">
+        <v>4500</v>
+      </c>
+      <c r="O57" s="3">
+        <v>2900</v>
+      </c>
+      <c r="P57" s="3">
+        <v>3000</v>
+      </c>
+      <c r="Q57" s="3">
         <v>2500</v>
       </c>
-      <c r="I57" s="3">
-        <v>1500</v>
-      </c>
-      <c r="J57" s="3">
-        <v>2600</v>
-      </c>
-      <c r="K57" s="3">
-        <v>2800</v>
-      </c>
-      <c r="L57" s="3">
-        <v>4500</v>
-      </c>
-      <c r="M57" s="3">
-        <v>2900</v>
-      </c>
-      <c r="N57" s="3">
-        <v>3000</v>
-      </c>
-      <c r="O57" s="3">
-        <v>2500</v>
-      </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>6500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>4000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>3200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>2700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>2400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>2300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>3700</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4133,31 +4394,37 @@
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>3</v>
+      <c r="D58" s="3">
+        <v>100</v>
+      </c>
+      <c r="E58" s="3">
+        <v>100</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G58" s="3">
-        <v>1600</v>
+        <v>300</v>
       </c>
       <c r="H58" s="3">
-        <v>1400</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
+        <v>200</v>
+      </c>
+      <c r="I58" s="3">
+        <v>200</v>
+      </c>
+      <c r="J58" s="3">
+        <v>400</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
@@ -4171,11 +4438,11 @@
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
-      <c r="P58" s="3">
-        <v>0</v>
+      <c r="O58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q58" s="3">
         <v>0</v>
@@ -4210,74 +4477,80 @@
       <c r="AA58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>44400</v>
+        <v>400</v>
       </c>
       <c r="E59" s="3">
-        <v>40000</v>
+        <v>400</v>
       </c>
       <c r="F59" s="3">
-        <v>42600</v>
+        <v>40100</v>
       </c>
       <c r="G59" s="3">
-        <v>40000</v>
+        <v>40900</v>
       </c>
       <c r="H59" s="3">
-        <v>41400</v>
+        <v>700</v>
       </c>
       <c r="I59" s="3">
+        <v>700</v>
+      </c>
+      <c r="J59" s="3">
+        <v>42800</v>
+      </c>
+      <c r="K59" s="3">
         <v>47500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>48800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>47700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>52600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>52500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>54000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>61600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>79300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>77300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>76600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>80800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>83400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>76400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>93500</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4287,74 +4560,80 @@
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>44500</v>
+      </c>
+      <c r="E60" s="3">
+        <v>43000</v>
+      </c>
+      <c r="F60" s="3">
+        <v>44600</v>
+      </c>
+      <c r="G60" s="3">
         <v>45400</v>
       </c>
-      <c r="E60" s="3">
-        <v>40900</v>
-      </c>
-      <c r="F60" s="3">
-        <v>43800</v>
-      </c>
-      <c r="G60" s="3">
-        <v>43800</v>
-      </c>
       <c r="H60" s="3">
-        <v>45400</v>
+        <v>39700</v>
       </c>
       <c r="I60" s="3">
+        <v>40000</v>
+      </c>
+      <c r="J60" s="3">
+        <v>48900</v>
+      </c>
+      <c r="K60" s="3">
         <v>49000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>51400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>50500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>57100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>55300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>57000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>64100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>85800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>81300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>79800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>83500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>85800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>78700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>97200</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4364,22 +4643,28 @@
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H61" s="3">
         <v>0</v>
@@ -4388,7 +4673,7 @@
         <v>0</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -4441,74 +4726,80 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>300</v>
-      </c>
-      <c r="E62" s="3">
-        <v>200</v>
-      </c>
-      <c r="F62" s="3">
-        <v>600</v>
-      </c>
-      <c r="G62" s="3">
-        <v>2000</v>
-      </c>
-      <c r="H62" s="3">
-        <v>1800</v>
-      </c>
-      <c r="I62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K62" s="3">
         <v>3800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>2600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>2700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>2800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>4100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>3300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>3700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>4200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>4300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>1100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>1100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>1200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>2100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>2800</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4518,8 +4809,14 @@
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4595,8 +4892,14 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4672,8 +4975,14 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4749,74 +5058,80 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>49300</v>
+        <v>44600</v>
       </c>
       <c r="E66" s="3">
+        <v>43000</v>
+      </c>
+      <c r="F66" s="3">
         <v>44900</v>
       </c>
-      <c r="F66" s="3">
-        <v>49200</v>
-      </c>
       <c r="G66" s="3">
-        <v>51600</v>
+        <v>45700</v>
       </c>
       <c r="H66" s="3">
+        <v>40000</v>
+      </c>
+      <c r="I66" s="3">
+        <v>40200</v>
+      </c>
+      <c r="J66" s="3">
+        <v>49500</v>
+      </c>
+      <c r="K66" s="3">
+        <v>58800</v>
+      </c>
+      <c r="L66" s="3">
+        <v>53900</v>
+      </c>
+      <c r="M66" s="3">
         <v>53200</v>
       </c>
-      <c r="I66" s="3">
-        <v>58800</v>
-      </c>
-      <c r="J66" s="3">
-        <v>53900</v>
-      </c>
-      <c r="K66" s="3">
-        <v>53200</v>
-      </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>59900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>59400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>60300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>67800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>89900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>85700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>80900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>84600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>87000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>80800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>100000</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4826,8 +5141,14 @@
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4855,8 +5176,10 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4932,8 +5255,14 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5009,8 +5338,14 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5066,17 +5401,17 @@
         <v>0</v>
       </c>
       <c r="U70" s="3">
+        <v>0</v>
+      </c>
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+      <c r="W70" s="3">
         <v>1261300</v>
       </c>
-      <c r="V70" s="3">
+      <c r="X70" s="3">
         <v>1040100</v>
       </c>
-      <c r="W70" s="3">
-        <v>0</v>
-      </c>
-      <c r="X70" s="3">
-        <v>0</v>
-      </c>
       <c r="Y70" s="3">
         <v>0</v>
       </c>
@@ -5086,8 +5421,14 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5163,74 +5504,80 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-1248100</v>
+        <v>-1265600</v>
       </c>
       <c r="E72" s="3">
-        <v>-1244800</v>
+        <v>-1221600</v>
       </c>
       <c r="F72" s="3">
-        <v>-1239600</v>
+        <v>-1226100</v>
       </c>
       <c r="G72" s="3">
-        <v>-1222600</v>
+        <v>-1248500</v>
       </c>
       <c r="H72" s="3">
-        <v>-1214500</v>
+        <v>-1210100</v>
       </c>
       <c r="I72" s="3">
+        <v>-1217500</v>
+      </c>
+      <c r="J72" s="3">
+        <v>-1280000</v>
+      </c>
+      <c r="K72" s="3">
         <v>-1182300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-1137700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-1101800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-1086100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-1112900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-1076800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-1126800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-1174900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-903900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-864900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-825000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-767100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-743400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-668400</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5240,8 +5587,14 @@
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5317,8 +5670,14 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5394,8 +5753,14 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5471,74 +5836,80 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>77900</v>
+      </c>
+      <c r="E76" s="3">
+        <v>75200</v>
+      </c>
+      <c r="F76" s="3">
+        <v>81500</v>
+      </c>
+      <c r="G76" s="3">
         <v>83000</v>
       </c>
-      <c r="E76" s="3">
-        <v>86000</v>
-      </c>
-      <c r="F76" s="3">
-        <v>89900</v>
-      </c>
-      <c r="G76" s="3">
-        <v>106700</v>
-      </c>
       <c r="H76" s="3">
-        <v>111300</v>
+        <v>83600</v>
       </c>
       <c r="I76" s="3">
+        <v>84100</v>
+      </c>
+      <c r="J76" s="3">
+        <v>92800</v>
+      </c>
+      <c r="K76" s="3">
         <v>144000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>189800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>201000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>214800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>236900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>263100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>291800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>329300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>575000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>623300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>615700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>604600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>-711600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>-642200</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5548,8 +5919,14 @@
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5625,167 +6002,185 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="I80" s="2">
+        <v>45107</v>
+      </c>
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
-        <v>44834</v>
-      </c>
-      <c r="H80" s="2">
-        <v>44651</v>
-      </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44469</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44377</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44286</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44196</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44104</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44012</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>43921</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>43830</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43738</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43646</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43555</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43465</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43373</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43281</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43190</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43100</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43008</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>42916</v>
       </c>
-      <c r="AA80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AC80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-3400</v>
+        <v>-1700</v>
       </c>
       <c r="E81" s="3">
-        <v>-5000</v>
+        <v>-1700</v>
       </c>
       <c r="F81" s="3">
-        <v>-17000</v>
+        <v>-1700</v>
       </c>
       <c r="G81" s="3">
-        <v>-8100</v>
+        <v>-1700</v>
       </c>
       <c r="H81" s="3">
-        <v>-31800</v>
+        <v>-2400</v>
       </c>
       <c r="I81" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="J81" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="K81" s="3">
         <v>-44900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-13500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-15000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-5100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-13300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-12400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-20900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-255900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-50300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-18800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-21400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-26300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-65900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-43300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>3700</v>
       </c>
-      <c r="X81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA81" s="3">
         <v>-63300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-49600</v>
       </c>
-      <c r="AA81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AC81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5813,31 +6208,33 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3">
-        <v>0</v>
+      <c r="D83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F83" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="G83" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="H83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I83" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J83" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -5866,32 +6263,38 @@
       <c r="S83" s="3">
         <v>0</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
+      <c r="T83" s="3">
+        <v>0</v>
       </c>
       <c r="U83" s="3">
+        <v>0</v>
+      </c>
+      <c r="V83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W83" s="3">
         <v>8500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>4500</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y83" s="3">
+      <c r="Y83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA83" s="3">
         <v>18700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>18900</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5967,8 +6370,14 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6044,8 +6453,14 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6121,8 +6536,14 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6198,8 +6619,14 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6275,85 +6702,97 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-1100</v>
+        <v>-2100</v>
       </c>
       <c r="E89" s="3">
-        <v>-4600</v>
+        <v>-2000</v>
       </c>
       <c r="F89" s="3">
-        <v>800</v>
+        <v>-500</v>
       </c>
       <c r="G89" s="3">
+        <v>-500</v>
+      </c>
+      <c r="H89" s="3">
         <v>-2300</v>
       </c>
-      <c r="H89" s="3">
-        <v>-5800</v>
-      </c>
       <c r="I89" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="J89" s="3">
+        <v>400</v>
+      </c>
+      <c r="K89" s="3">
         <v>-8800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-1600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-6900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>1700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-4500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-1200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-22800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-5900</v>
-      </c>
-      <c r="Q89" s="3">
-        <v>-13800</v>
-      </c>
-      <c r="R89" s="3">
-        <v>-4700</v>
       </c>
       <c r="S89" s="3">
         <v>-13800</v>
       </c>
       <c r="T89" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="U89" s="3">
+        <v>-13800</v>
+      </c>
+      <c r="V89" s="3">
         <v>4200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-35800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-2500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-19700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-18600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>26100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-33900</v>
       </c>
-      <c r="AA89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6381,31 +6820,33 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F91" s="3">
-        <v>0</v>
+        <v>-6500</v>
       </c>
       <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
+        <v>-6600</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J91" s="3">
-        <v>0</v>
+        <v>-4000</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -6434,32 +6875,38 @@
       <c r="S91" s="3">
         <v>0</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>3</v>
+      <c r="T91" s="3">
+        <v>0</v>
       </c>
       <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W91" s="3">
         <v>-200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-200</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y91" s="3">
+      <c r="Y91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-300</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6535,8 +6982,14 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6612,85 +7065,97 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-17400</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-16800</v>
+      </c>
+      <c r="F94" s="3">
         <v>100</v>
       </c>
-      <c r="E94" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="F94" s="3">
-        <v>4100</v>
-      </c>
       <c r="G94" s="3">
-        <v>-4000</v>
+        <v>100</v>
       </c>
       <c r="H94" s="3">
-        <v>-5000</v>
+        <v>-1400</v>
       </c>
       <c r="I94" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="J94" s="3">
+        <v>2100</v>
+      </c>
+      <c r="K94" s="3">
         <v>-4600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>11600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-8300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>13000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-16600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-2000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>20900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>2000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-22900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-18600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>21400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-11400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-12800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-7900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>11800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>33600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>11500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-6800</v>
       </c>
-      <c r="AA94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6718,31 +7183,33 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -6795,8 +7262,14 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6872,8 +7345,14 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6949,8 +7428,14 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7026,235 +7511,259 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J100" s="3">
+        <v>-700</v>
+      </c>
+      <c r="K100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L100" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="M100" s="3">
         <v>-1300</v>
       </c>
-      <c r="G100" s="3">
-        <v>-400</v>
-      </c>
-      <c r="H100" s="3">
-        <v>1200</v>
-      </c>
-      <c r="I100" s="3">
-        <v>-100</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="N100" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="O100" s="3">
+        <v>-13800</v>
+      </c>
+      <c r="P100" s="3">
+        <v>-800</v>
+      </c>
+      <c r="Q100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="R100" s="3">
+        <v>-300</v>
+      </c>
+      <c r="S100" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="T100" s="3">
         <v>-1100</v>
       </c>
-      <c r="K100" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="L100" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="M100" s="3">
-        <v>-13800</v>
-      </c>
-      <c r="N100" s="3">
-        <v>-800</v>
-      </c>
-      <c r="O100" s="3">
-        <v>-200</v>
-      </c>
-      <c r="P100" s="3">
-        <v>-300</v>
-      </c>
-      <c r="Q100" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="R100" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-3500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>61800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>1600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>200</v>
       </c>
-      <c r="AA100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>200</v>
+      </c>
+      <c r="E101" s="3">
+        <v>200</v>
+      </c>
+      <c r="F101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="G101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="H101" s="3">
+        <v>100</v>
+      </c>
+      <c r="I101" s="3">
+        <v>100</v>
+      </c>
+      <c r="J101" s="3">
         <v>-100</v>
       </c>
-      <c r="E101" s="3">
-        <v>500</v>
-      </c>
-      <c r="F101" s="3">
-        <v>-300</v>
-      </c>
-      <c r="G101" s="3">
-        <v>200</v>
-      </c>
-      <c r="H101" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3">
         <v>-400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-1500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-1600</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
         <v>800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>2700</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>2600</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-2500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>-200</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>3900</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>5200</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>-4400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>-2300</v>
       </c>
-      <c r="AA101" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-1000</v>
+        <v>-19600</v>
       </c>
       <c r="E102" s="3">
-        <v>-7100</v>
+        <v>-18900</v>
       </c>
       <c r="F102" s="3">
-        <v>3300</v>
+        <v>-500</v>
       </c>
       <c r="G102" s="3">
-        <v>-6400</v>
+        <v>-500</v>
       </c>
       <c r="H102" s="3">
-        <v>-9600</v>
+        <v>-3500</v>
       </c>
       <c r="I102" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="J102" s="3">
+        <v>1700</v>
+      </c>
+      <c r="K102" s="3">
         <v>-13400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>8500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-16200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>12100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-36400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-4000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-1300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-36900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-21700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>1600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>54400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-43200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-5000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-12100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>13400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>35100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-42800</v>
       </c>
-      <c r="AA102" s="3" t="s">
+      <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MOGU_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MOGU_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="92">
   <si>
     <t>MOGU</t>
   </si>
@@ -656,379 +656,404 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AC7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AE7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>4400</v>
+        <v>5500</v>
       </c>
       <c r="E8" s="3">
-        <v>4300</v>
-      </c>
-      <c r="F8" s="3">
+        <v>5400</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="3">
         <v>5300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>5400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K8" s="3">
         <v>5700</v>
       </c>
-      <c r="I8" s="3">
-        <v>5700</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>8500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>10900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>13000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>12600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>20200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>16000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>18400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>17500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>42200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>30500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>38800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>33100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>53300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>33900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>35800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>26900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>45300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>32000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>39300</v>
       </c>
-      <c r="AC8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AE8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>2800</v>
+        <v>3100</v>
       </c>
       <c r="E9" s="3">
-        <v>2700</v>
-      </c>
-      <c r="F9" s="3">
+        <v>3100</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H9" s="3">
         <v>2900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>2900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K9" s="3">
         <v>3400</v>
       </c>
-      <c r="I9" s="3">
-        <v>3400</v>
-      </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>3900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>5900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>6100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>5200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>7000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>6500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>6800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>8600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>15400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>11700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>9500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>9300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>14600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>11500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>10300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>10900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>12300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>11600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>12000</v>
       </c>
-      <c r="AC9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AE9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>1600</v>
+        <v>2400</v>
       </c>
       <c r="E10" s="3">
-        <v>1500</v>
-      </c>
-      <c r="F10" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H10" s="3">
         <v>2500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>2500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K10" s="3">
         <v>2300</v>
       </c>
-      <c r="I10" s="3">
-        <v>2300</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>4600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>5100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>6800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>7300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>13200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>9500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>11700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>8900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>26800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>18800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>29400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>23800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>38700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>22500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>25600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>16000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>33000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>20400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>27300</v>
       </c>
-      <c r="AC10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AE10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1058,91 +1083,99 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H12" s="3">
         <v>900</v>
       </c>
-      <c r="E12" s="3">
-        <v>800</v>
-      </c>
-      <c r="F12" s="3">
+      <c r="I12" s="3">
         <v>900</v>
       </c>
-      <c r="G12" s="3">
-        <v>900</v>
-      </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K12" s="3">
         <v>1000</v>
       </c>
-      <c r="I12" s="3">
-        <v>1000</v>
-      </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>1200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>3300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>3100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>2700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>3800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>3900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>4000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>4800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>5000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>7700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>8800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>8700</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>8000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>8800</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>8800</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>10000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>10500</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>11300</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>10800</v>
       </c>
-      <c r="AC12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1224,41 +1257,47 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
+      <c r="D14" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E14" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3">
         <v>700</v>
       </c>
-      <c r="I14" s="3">
-        <v>700</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>6100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>26300</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1268,47 +1307,53 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>216400</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>3</v>
+      <c r="X14" s="3">
+        <v>0</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="Z14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>-2000</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC14" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1325,73 +1370,79 @@
         <v>0</v>
       </c>
       <c r="H15" s="3">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3">
+        <v>0</v>
+      </c>
+      <c r="K15" s="3">
         <v>100</v>
       </c>
-      <c r="I15" s="3">
-        <v>100</v>
-      </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>2900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>13500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>9100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>11300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>15700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>10800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>9800</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>12800</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>16100</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>11800</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>10100</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>6800</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>9700</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Y15" s="3">
         <v>8000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Z15" s="3">
         <v>3900</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AA15" s="3">
         <v>7900</v>
-      </c>
-      <c r="Z15" s="3">
-        <v>16300</v>
-      </c>
-      <c r="AA15" s="3">
-        <v>16300</v>
       </c>
       <c r="AB15" s="3">
         <v>16300</v>
       </c>
-      <c r="AC15" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>16300</v>
+      </c>
+      <c r="AD15" s="3">
+        <v>16300</v>
+      </c>
+      <c r="AE15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1418,174 +1469,188 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E17" s="3">
+        <v>8300</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H17" s="3">
+        <v>7200</v>
+      </c>
+      <c r="I17" s="3">
         <v>7400</v>
       </c>
-      <c r="E17" s="3">
-        <v>7100</v>
-      </c>
-      <c r="F17" s="3">
-        <v>7200</v>
-      </c>
-      <c r="G17" s="3">
-        <v>7400</v>
-      </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K17" s="3">
         <v>8600</v>
       </c>
-      <c r="I17" s="3">
-        <v>8600</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>11900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>57800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>26800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>27800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>37300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>30300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>31700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>39500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>291900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>64900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>55300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>58700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>67500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>61800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>52100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>47900</v>
       </c>
-      <c r="Z17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC17" s="3">
         <v>76000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>69400</v>
       </c>
-      <c r="AC17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AE17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-3000</v>
+        <v>-2900</v>
       </c>
       <c r="E18" s="3">
         <v>-2900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="F18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H18" s="3">
         <v>-1900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-1900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K18" s="3">
         <v>-2900</v>
       </c>
-      <c r="I18" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-3400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-46800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-13800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-15200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-17000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-14300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-13200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-22000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-249700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-34400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-16400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-25600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-14200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-27900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-16300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-20900</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC18" s="3">
         <v>-44000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-30100</v>
       </c>
-      <c r="AC18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AE18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1615,91 +1680,99 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3">
+        <v>100</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="3">
         <v>200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>200</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="J20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>1800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>300</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>13300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-4100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-3900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>1300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>1400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>5700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>1300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>1100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>23700</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC20" s="3">
         <v>1900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>900</v>
       </c>
-      <c r="AC20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AE20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1707,108 +1780,114 @@
         <v>-3000</v>
       </c>
       <c r="E21" s="3">
-        <v>-2900</v>
+        <v>-3000</v>
       </c>
       <c r="F21" s="3">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3">
         <v>-2000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-2100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
+        <v>0</v>
+      </c>
+      <c r="K21" s="3">
         <v>-2800</v>
       </c>
-      <c r="I21" s="3">
-        <v>-2800</v>
-      </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-1000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-40700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-4200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-20000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>1800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-12700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-23400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-249700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-36400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-4800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-3300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-11600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-18100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-10700</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA21" s="3">
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC21" s="3">
         <v>-23300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>-10300</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AE21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
-      </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="D22" s="3">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1864,174 +1943,192 @@
       <c r="AC22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-1600</v>
+        <v>-2600</v>
       </c>
       <c r="E23" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="F23" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H23" s="3">
         <v>-1700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-1700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K23" s="3">
         <v>-3000</v>
       </c>
-      <c r="I23" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-9400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-45100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-13500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-15300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-3800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-13500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-12500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-21100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-253800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-38300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-15100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-24200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-8500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-26600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-15200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>2700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-26800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-42100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-29200</v>
       </c>
-      <c r="AC23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AE23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K24" s="3">
         <v>-100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="L24" s="3">
         <v>-100</v>
       </c>
-      <c r="J24" s="3">
-        <v>-100</v>
-      </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>-200</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>-300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>1300</v>
-      </c>
-      <c r="O24" s="3">
-        <v>-200</v>
-      </c>
-      <c r="P24" s="3">
-        <v>-200</v>
       </c>
       <c r="Q24" s="3">
         <v>-200</v>
       </c>
       <c r="R24" s="3">
-        <v>100</v>
+        <v>-200</v>
       </c>
       <c r="S24" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="T24" s="3">
         <v>100</v>
       </c>
       <c r="U24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="V24" s="3">
+        <v>100</v>
+      </c>
+      <c r="W24" s="3">
         <v>-700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>-300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>-800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>-700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>-1700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>-3700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>-3900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>-3800</v>
       </c>
-      <c r="AC24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AE24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2113,174 +2210,192 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-1600</v>
+        <v>-2600</v>
       </c>
       <c r="E26" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="F26" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H26" s="3">
         <v>-1700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-1700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K26" s="3">
         <v>-2900</v>
       </c>
-      <c r="I26" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-9300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-44800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-13500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-15000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-5100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-13300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-12400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-20900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-254000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-38200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-15200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-23400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-8300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-25800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-14500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>4400</v>
       </c>
-      <c r="Z26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC26" s="3">
         <v>-38200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-25300</v>
       </c>
-      <c r="AC26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AE26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H27" s="3">
         <v>-1700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="I27" s="3">
         <v>-1700</v>
       </c>
-      <c r="F27" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K27" s="3">
         <v>-2400</v>
       </c>
-      <c r="I27" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-8800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-44900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-13500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-15000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-5100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-13300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-12400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-20900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-255900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-50300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-18800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-21400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-26300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-65900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-43300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>3700</v>
       </c>
-      <c r="Z27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC27" s="3">
         <v>-63300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-49600</v>
       </c>
-      <c r="AC27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AE27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2362,8 +2477,14 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2445,8 +2566,14 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2528,8 +2655,14 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2611,174 +2744,192 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H32" s="3">
         <v>-200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-200</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="J32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-1800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-300</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-13300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>4100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>3900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-1300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-1400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-5700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-1300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-23700</v>
       </c>
-      <c r="Z32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC32" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-900</v>
       </c>
-      <c r="AC32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AE32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H33" s="3">
         <v>-1700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="I33" s="3">
         <v>-1700</v>
       </c>
-      <c r="F33" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K33" s="3">
         <v>-2400</v>
       </c>
-      <c r="I33" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-8800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-44900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-13500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-15000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-5100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-13300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-12400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-20900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-255900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-50300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-18800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-21400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-26300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-65900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-43300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>3700</v>
       </c>
-      <c r="Z33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC33" s="3">
         <v>-63300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-49600</v>
       </c>
-      <c r="AC33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AE33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2860,179 +3011,197 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H35" s="3">
         <v>-1700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="I35" s="3">
         <v>-1700</v>
       </c>
-      <c r="F35" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K35" s="3">
         <v>-2400</v>
       </c>
-      <c r="I35" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-8800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-44900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-13500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-15000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-5100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-13300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-12400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-20900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-255900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-50300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-18800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-21400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-26300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-65900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-43300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>3700</v>
       </c>
-      <c r="Z35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC35" s="3">
         <v>-63300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-49600</v>
       </c>
-      <c r="AC35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AE35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AC38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AE38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3062,8 +3231,10 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3093,80 +3264,82 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>12000</v>
+        <v>11300</v>
       </c>
       <c r="E41" s="3">
-        <v>11600</v>
-      </c>
-      <c r="F41" s="3">
+        <v>11200</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H41" s="3">
         <v>49700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>50600</v>
       </c>
-      <c r="H41" s="3">
-        <v>50200</v>
-      </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K41" s="3">
         <v>50500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>60600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>71500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>84900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>74900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>91000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>81300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>115200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>126200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>135500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>138300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>177500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>194200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>183900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>129500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>166400</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3176,80 +3349,86 @@
       <c r="AC41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>38700</v>
+        <v>41100</v>
       </c>
       <c r="E42" s="3">
-        <v>37400</v>
+        <v>40900</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>8600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>8700</v>
       </c>
-      <c r="H42" s="3">
-        <v>14200</v>
-      </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>14300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>21600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>15300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>24400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>36000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>22100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>32700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>30600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>35100</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>50900</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>59900</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>50500</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>32200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>50400</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>44400</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>32200</v>
       </c>
-      <c r="Y42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3259,80 +3438,86 @@
       <c r="AC42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>4100</v>
+        <v>13800</v>
       </c>
       <c r="E43" s="3">
-        <v>4000</v>
-      </c>
-      <c r="F43" s="3">
+        <v>13800</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H43" s="3">
         <v>7900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>8000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K43" s="3">
         <v>600</v>
       </c>
-      <c r="I43" s="3">
-        <v>600</v>
-      </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>10600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>11700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>13900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>17600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>19400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>16100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>16500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>16700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>27900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>21600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>18900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>18700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>19200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>27400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>30000</v>
       </c>
-      <c r="Y43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3342,8 +3527,14 @@
       <c r="AC43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3353,11 +3544,11 @@
       <c r="E44" s="3">
         <v>0</v>
       </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H44" s="3">
         <v>0</v>
@@ -3365,8 +3556,8 @@
       <c r="I44" s="3">
         <v>0</v>
       </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3378,44 +3569,44 @@
         <v>0</v>
       </c>
       <c r="N44" s="3">
+        <v>0</v>
+      </c>
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+      <c r="P44" s="3">
         <v>100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>2200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>100</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>100</v>
       </c>
-      <c r="Y44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3425,80 +3616,86 @@
       <c r="AC44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>13600</v>
+        <v>300</v>
       </c>
       <c r="E45" s="3">
-        <v>13200</v>
-      </c>
-      <c r="F45" s="3">
+        <v>300</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3">
         <v>500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>500</v>
       </c>
-      <c r="H45" s="3">
-        <v>13600</v>
-      </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3">
         <v>13700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>1000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>8700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>9300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>7900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>13800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>11800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>11800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>14700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>18600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>22100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>24400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>24700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>23900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>7300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>6300</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3508,80 +3705,86 @@
       <c r="AC45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>68600</v>
+        <v>66900</v>
       </c>
       <c r="E46" s="3">
-        <v>66200</v>
-      </c>
-      <c r="F46" s="3">
+        <v>66500</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H46" s="3">
         <v>70300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>71600</v>
       </c>
-      <c r="H46" s="3">
-        <v>78700</v>
-      </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K46" s="3">
         <v>79200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>96900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>107200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>132500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>136400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>146400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>142100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>174500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>193100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>235000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>242400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>272100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>270600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>278000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>208700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>234900</v>
       </c>
-      <c r="Y46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3591,80 +3794,86 @@
       <c r="AC46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>7700</v>
+        <v>6900</v>
       </c>
       <c r="E47" s="3">
-        <v>7400</v>
-      </c>
-      <c r="F47" s="3">
-        <v>11300</v>
-      </c>
-      <c r="G47" s="3">
-        <v>11500</v>
+        <v>6800</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H47" s="3">
         <v>11300</v>
       </c>
       <c r="I47" s="3">
+        <v>11500</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K47" s="3">
         <v>11300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>10100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>11200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>10300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>9200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>8600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>17200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>15900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>15100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>11300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>17300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>34200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>36800</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>32000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>29200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>27600</v>
       </c>
-      <c r="Y47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3674,80 +3883,86 @@
       <c r="AC47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>43000</v>
+        <v>38900</v>
       </c>
       <c r="E48" s="3">
-        <v>41500</v>
-      </c>
-      <c r="F48" s="3">
+        <v>38700</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H48" s="3">
         <v>41900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>42600</v>
       </c>
-      <c r="H48" s="3">
-        <v>30800</v>
-      </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K48" s="3">
         <v>30900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>29100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>1400</v>
-      </c>
-      <c r="L48" s="3">
-        <v>1500</v>
-      </c>
-      <c r="M48" s="3">
-        <v>1500</v>
       </c>
       <c r="N48" s="3">
         <v>1500</v>
       </c>
       <c r="O48" s="3">
+        <v>1500</v>
+      </c>
+      <c r="P48" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Q48" s="3">
         <v>2000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>1800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>2100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>2300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>2400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>2100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>1800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>1600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>1500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>1700</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3757,8 +3972,14 @@
       <c r="AC48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3768,11 +3989,11 @@
       <c r="E49" s="3">
         <v>100</v>
       </c>
-      <c r="F49" s="3">
-        <v>100</v>
-      </c>
-      <c r="G49" s="3">
-        <v>100</v>
+      <c r="F49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H49" s="3">
         <v>100</v>
@@ -3780,57 +4001,57 @@
       <c r="I49" s="3">
         <v>100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="J49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K49" s="3">
+        <v>100</v>
+      </c>
+      <c r="L49" s="3">
         <v>1800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>52700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>76400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>84600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>95600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>117800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>129200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>147300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>168300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>396000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>395600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>391000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>378700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>388200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>232000</v>
       </c>
-      <c r="Y49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3840,8 +4061,14 @@
       <c r="AC49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3923,8 +4150,14 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4006,80 +4239,86 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>7000</v>
+        <v>5500</v>
       </c>
       <c r="E52" s="3">
-        <v>6800</v>
-      </c>
-      <c r="F52" s="3">
+        <v>5400</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H52" s="3">
         <v>6300</v>
-      </c>
-      <c r="G52" s="3">
-        <v>6400</v>
-      </c>
-      <c r="H52" s="3">
-        <v>6400</v>
       </c>
       <c r="I52" s="3">
         <v>6400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="J52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K52" s="3">
+        <v>6400</v>
+      </c>
+      <c r="L52" s="3">
         <v>9300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>30400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>23100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>22500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>22500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>17200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>2000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>2100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>2200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>2700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>1300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>2900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>1600</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4089,8 +4328,14 @@
       <c r="AC52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4172,80 +4417,86 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>126500</v>
+        <v>118300</v>
       </c>
       <c r="E54" s="3">
-        <v>122100</v>
-      </c>
-      <c r="F54" s="3">
+        <v>117600</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H54" s="3">
         <v>130000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>132300</v>
       </c>
-      <c r="H54" s="3">
-        <v>127200</v>
-      </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K54" s="3">
         <v>128000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>147200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>202800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>243700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>254200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>274700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>296300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>323400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>359700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>419200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>660700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>704100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>700300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>691600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>630600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>497800</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4255,8 +4506,14 @@
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4286,8 +4543,10 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4317,80 +4576,82 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="E57" s="3">
-        <v>500</v>
-      </c>
-      <c r="F57" s="3">
+        <v>600</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H57" s="3">
         <v>1000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>1000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K57" s="3">
         <v>900</v>
       </c>
-      <c r="I57" s="3">
-        <v>900</v>
-      </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>1200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>1500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>2600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>2800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>4500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>2900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>3000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>2500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>6500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>4000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>3200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>2700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>2400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>2300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>3700</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4400,8 +4661,14 @@
       <c r="AC57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4411,27 +4678,27 @@
       <c r="E58" s="3">
         <v>100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="F58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H58" s="3">
         <v>300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K58" s="3">
         <v>200</v>
       </c>
-      <c r="I58" s="3">
-        <v>200</v>
-      </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>400</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4444,11 +4711,11 @@
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
-      <c r="R58" s="3">
-        <v>0</v>
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S58" s="3">
         <v>0</v>
@@ -4483,80 +4750,86 @@
       <c r="AC58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>400</v>
+        <v>39700</v>
       </c>
       <c r="E59" s="3">
-        <v>400</v>
-      </c>
-      <c r="F59" s="3">
+        <v>39500</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H59" s="3">
         <v>40100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>40900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K59" s="3">
         <v>700</v>
       </c>
-      <c r="I59" s="3">
-        <v>700</v>
-      </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>42800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>47500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>48800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>47700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>52600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>52500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>54000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>61600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>79300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>77300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>76600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>80800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>83400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>76400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>93500</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4566,80 +4839,86 @@
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>44500</v>
+        <v>44200</v>
       </c>
       <c r="E60" s="3">
-        <v>43000</v>
-      </c>
-      <c r="F60" s="3">
+        <v>44000</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H60" s="3">
         <v>44600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>45400</v>
       </c>
-      <c r="H60" s="3">
-        <v>39700</v>
-      </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K60" s="3">
         <v>40000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>48900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>49000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>51400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>50500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>57100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>55300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>57000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>64100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>85800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>81300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>79800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>83500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>85800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>78700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>97200</v>
       </c>
-      <c r="Y60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4649,38 +4928,44 @@
       <c r="AC60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3">
+        <v>0</v>
+      </c>
+      <c r="G61" s="3">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3">
         <v>100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="I61" s="3">
         <v>100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="J61" s="3">
+        <v>0</v>
+      </c>
+      <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
         <v>100</v>
       </c>
-      <c r="G61" s="3">
-        <v>100</v>
-      </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
-      <c r="J61" s="3">
-        <v>100</v>
-      </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -4732,8 +5017,14 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4758,54 +5049,54 @@
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M62" s="3">
         <v>3800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>2600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>2700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>2800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>4100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>3300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>3700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>4200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>4300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>1100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>1100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>1200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>2100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>2800</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4815,8 +5106,14 @@
       <c r="AC62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4898,8 +5195,14 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4981,8 +5284,14 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5064,80 +5373,86 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>44600</v>
+        <v>44300</v>
       </c>
       <c r="E66" s="3">
-        <v>43000</v>
-      </c>
-      <c r="F66" s="3">
+        <v>44000</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H66" s="3">
         <v>44900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>45700</v>
       </c>
-      <c r="H66" s="3">
-        <v>40000</v>
-      </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K66" s="3">
         <v>40200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>49500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>58800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>53900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>53200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>59900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>59400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>60300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>67800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>89900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>85700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>80900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>84600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>87000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>80800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>100000</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5147,8 +5462,14 @@
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5178,8 +5499,10 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5261,8 +5584,14 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5344,8 +5673,14 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5407,17 +5742,17 @@
         <v>0</v>
       </c>
       <c r="W70" s="3">
+        <v>0</v>
+      </c>
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="3">
         <v>1261300</v>
       </c>
-      <c r="X70" s="3">
+      <c r="Z70" s="3">
         <v>1040100</v>
       </c>
-      <c r="Y70" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z70" s="3">
-        <v>0</v>
-      </c>
       <c r="AA70" s="3">
         <v>0</v>
       </c>
@@ -5427,8 +5762,14 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5510,80 +5851,86 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-1265600</v>
+        <v>-1228700</v>
       </c>
       <c r="E72" s="3">
-        <v>-1221600</v>
-      </c>
-      <c r="F72" s="3">
+        <v>-1221500</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H72" s="3">
         <v>-1226100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-1248500</v>
       </c>
-      <c r="H72" s="3">
-        <v>-1210100</v>
-      </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K72" s="3">
         <v>-1217500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-1280000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-1182300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-1137700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-1101800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-1086100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-1112900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-1076800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-1126800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-1174900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-903900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-864900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-825000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-767100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-743400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-668400</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5593,8 +5940,14 @@
       <c r="AC72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5676,8 +6029,14 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5759,8 +6118,14 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5842,80 +6207,86 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>77900</v>
+        <v>70100</v>
       </c>
       <c r="E76" s="3">
-        <v>75200</v>
-      </c>
-      <c r="F76" s="3">
+        <v>69700</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H76" s="3">
         <v>81500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>83000</v>
       </c>
-      <c r="H76" s="3">
-        <v>83600</v>
-      </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K76" s="3">
         <v>84100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>92800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>144000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>189800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>201000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>214800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>236900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>263100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>291800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>329300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>575000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>623300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>615700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>604600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>-711600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>-642200</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5925,8 +6296,14 @@
       <c r="AC76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6008,179 +6385,197 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AC80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AE80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H81" s="3">
         <v>-1700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="I81" s="3">
         <v>-1700</v>
       </c>
-      <c r="F81" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K81" s="3">
         <v>-2400</v>
       </c>
-      <c r="I81" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-8800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-44900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-13500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-15000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-5100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-13300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-12400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-20900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-255900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-50300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-18800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-21400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-26300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-65900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-43300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>3700</v>
       </c>
-      <c r="Z81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC81" s="3">
         <v>-63300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-49600</v>
       </c>
-      <c r="AC81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AE81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6210,38 +6605,40 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F83" s="3">
-        <v>400</v>
-      </c>
-      <c r="G83" s="3">
-        <v>400</v>
+      <c r="D83" s="3">
+        <v>600</v>
+      </c>
+      <c r="E83" s="3">
+        <v>600</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H83" s="3">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="I83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K83" s="3">
         <v>200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>200</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
       <c r="M83" s="3">
         <v>0</v>
       </c>
@@ -6269,32 +6666,38 @@
       <c r="U83" s="3">
         <v>0</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>3</v>
+      <c r="V83" s="3">
+        <v>0</v>
       </c>
       <c r="W83" s="3">
+        <v>0</v>
+      </c>
+      <c r="X83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y83" s="3">
         <v>8500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>4500</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA83" s="3">
+      <c r="AA83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC83" s="3">
         <v>18700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>18900</v>
       </c>
-      <c r="AC83" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6376,8 +6779,14 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6459,8 +6868,14 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6542,8 +6957,14 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6625,8 +7046,14 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6708,91 +7135,103 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-2100</v>
+        <v>-2700</v>
       </c>
       <c r="E89" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="F89" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H89" s="3">
         <v>-500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K89" s="3">
         <v>-2300</v>
       </c>
-      <c r="I89" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-8800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-1600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-6900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>1700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-4500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-22800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-5900</v>
-      </c>
-      <c r="S89" s="3">
-        <v>-13800</v>
-      </c>
-      <c r="T89" s="3">
-        <v>-4700</v>
       </c>
       <c r="U89" s="3">
         <v>-13800</v>
       </c>
       <c r="V89" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="W89" s="3">
+        <v>-13800</v>
+      </c>
+      <c r="X89" s="3">
         <v>4200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-35800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-19700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-18600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>26100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-33900</v>
       </c>
-      <c r="AC89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AE89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6822,38 +7261,40 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F91" s="3">
+      <c r="D91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H91" s="3">
         <v>-6500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-6600</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J91" s="3">
+      <c r="J91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L91" s="3">
         <v>-4000</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
@@ -6881,32 +7322,38 @@
       <c r="U91" s="3">
         <v>0</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>3</v>
+      <c r="V91" s="3">
+        <v>0</v>
       </c>
       <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-200</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA91" s="3">
+      <c r="AA91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-300</v>
       </c>
-      <c r="AC91" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6988,8 +7435,14 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7071,91 +7524,103 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-17400</v>
+        <v>2500</v>
       </c>
       <c r="E94" s="3">
-        <v>-16800</v>
-      </c>
-      <c r="F94" s="3">
+        <v>2500</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H94" s="3">
         <v>100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K94" s="3">
         <v>-1400</v>
       </c>
-      <c r="I94" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>2100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-4600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>11600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-8300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>13000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-16600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>20900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>2000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-22900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-18600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>21400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-11400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-12800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-7900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>11800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>33600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>11500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-6800</v>
       </c>
-      <c r="AC94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7185,8 +7650,10 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7211,11 +7678,11 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -7268,8 +7735,14 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7351,8 +7824,14 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7434,8 +7913,14 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7517,253 +8002,277 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L100" s="3">
+        <v>-700</v>
+      </c>
+      <c r="M100" s="3">
         <v>-100</v>
       </c>
-      <c r="E100" s="3">
-        <v>-100</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J100" s="3">
-        <v>-700</v>
-      </c>
-      <c r="K100" s="3">
-        <v>-100</v>
-      </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-1100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-1300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-1000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-13800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-2900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-1100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-3500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>61800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>1600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>200</v>
       </c>
-      <c r="AC100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AE100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>200</v>
+        <v>-100</v>
       </c>
       <c r="E101" s="3">
-        <v>200</v>
-      </c>
-      <c r="F101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3">
         <v>-200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K101" s="3">
         <v>100</v>
       </c>
-      <c r="I101" s="3">
-        <v>100</v>
-      </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-100</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
         <v>-400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-1500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-1600</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3">
         <v>800</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>-900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>2700</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>2600</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>-2500</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>-200</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>3900</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>5200</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>-4400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>-2300</v>
       </c>
-      <c r="AC101" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-19600</v>
+        <v>-200</v>
       </c>
       <c r="E102" s="3">
-        <v>-18900</v>
+        <v>-200</v>
       </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
         <v>-500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>-3500</v>
       </c>
-      <c r="I102" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>1700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-13400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>8500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-16200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>12100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-36400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-1300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-5100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-36900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-21700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>1600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>54400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-43200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-5000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-12100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>13400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>35100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-42800</v>
       </c>
-      <c r="AC102" s="3" t="s">
+      <c r="AE102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
